--- a/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>164 JEAN PIAGET</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.01357</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.83749</v>
-      </c>
-      <c r="I2" t="n">
-        <v>324</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.01357</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.83749</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>1252 SANTA ISABEL</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.03596</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.90168</v>
-      </c>
-      <c r="I3" t="n">
-        <v>863</v>
-      </c>
-      <c r="J3" t="n">
-        <v>41</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.03596</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.90168</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>1281 SANTA MARIA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.04287</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.92451</v>
-      </c>
-      <c r="I4" t="n">
-        <v>301</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.04287</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.92451</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>1249 JAVIER HERAUD</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.02791</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.91513999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>327</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.02791</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.91514</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>1237 JORGE D. GILES LLANOS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.01951</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.83795000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1259</v>
-      </c>
-      <c r="J6" t="n">
-        <v>48</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.01951</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.83795</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>1263 PURUCHUCO</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.04869</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.93006</v>
-      </c>
-      <c r="I7" t="n">
-        <v>902</v>
-      </c>
-      <c r="J7" t="n">
-        <v>42</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.04869</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.93006</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>191</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.04295</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.8978</v>
-      </c>
-      <c r="I8" t="n">
-        <v>335</v>
-      </c>
-      <c r="J8" t="n">
-        <v>13</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.04295</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.8978</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>1262 EL AMAUTA JOSE C. MARIATEGUI</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.04274</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.89803999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1359</v>
-      </c>
-      <c r="J9" t="n">
-        <v>50</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.04274</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.89804</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>1247</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.04497</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.91522999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>331</v>
-      </c>
-      <c r="J10" t="n">
-        <v>14</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.04497</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.91523</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>192 SANTA ROSITA DE LIMA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.04855</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.92995000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>213</v>
-      </c>
-      <c r="J11" t="n">
-        <v>9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.04855</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.92995</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>134</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.02871</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.92471</v>
-      </c>
-      <c r="I12" t="n">
-        <v>337</v>
-      </c>
-      <c r="J12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.02871</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.92471</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>0029 MARCO PUENTE LLANOS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.0312</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.92155</v>
-      </c>
-      <c r="I13" t="n">
-        <v>914</v>
-      </c>
-      <c r="J13" t="n">
-        <v>44</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.0312</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.92155</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>COLEGIO NACIONAL MIXTO HUAYCAN</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.01531</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.82682</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1660</v>
-      </c>
-      <c r="J14" t="n">
-        <v>62</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.01531</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.82682</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>1215 SAN JUAN PARIACHI</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.01066</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.8694</v>
-      </c>
-      <c r="I15" t="n">
-        <v>666</v>
-      </c>
-      <c r="J15" t="n">
-        <v>28</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.01066</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.8694</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>500 EL BOSQUE</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.06206</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.98335</v>
-      </c>
-      <c r="I16" t="n">
-        <v>361</v>
-      </c>
-      <c r="J16" t="n">
-        <v>13</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.06206</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.98335</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>0074 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.07036</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.98429</v>
-      </c>
-      <c r="I17" t="n">
-        <v>674</v>
-      </c>
-      <c r="J17" t="n">
-        <v>40</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.07036</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.98429</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>1258 SEBASTIAN LORENTE</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.01452</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.82606</v>
-      </c>
-      <c r="I18" t="n">
-        <v>754</v>
-      </c>
-      <c r="J18" t="n">
-        <v>30</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.01452</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.82606</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>1243 SAN ROQUE</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.02021</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.90613999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>276</v>
-      </c>
-      <c r="J19" t="n">
-        <v>13</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.02021</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.90614</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>135 NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.0733</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.98087</v>
-      </c>
-      <c r="I20" t="n">
-        <v>267</v>
-      </c>
-      <c r="J20" t="n">
-        <v>14</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.0733</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.98087</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>1142</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.02864</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.92962</v>
-      </c>
-      <c r="I21" t="n">
-        <v>580</v>
-      </c>
-      <c r="J21" t="n">
-        <v>29</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.02864</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.92962</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>1251 PERUANO SUIZO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.02194</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.8717</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1269</v>
-      </c>
-      <c r="J22" t="n">
-        <v>61</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.02194</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.8717</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>1245 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.01519</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.82089000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>979</v>
-      </c>
-      <c r="J23" t="n">
-        <v>42</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.01519</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.82089</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>1229 CAP. JULIO A. PONCE ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.05782</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.95716</v>
-      </c>
-      <c r="I24" t="n">
-        <v>989</v>
-      </c>
-      <c r="J24" t="n">
-        <v>44</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.05782</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.95716</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>1265 SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.00932</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.816</v>
-      </c>
-      <c r="I25" t="n">
-        <v>285</v>
-      </c>
-      <c r="J25" t="n">
-        <v>13</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.00932</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.816</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>1226</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.03692</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.93268</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1155</v>
-      </c>
-      <c r="J26" t="n">
-        <v>54</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.03692</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.93268</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>NUESTRA SEÑORA DE LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.07297</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.98454</v>
-      </c>
-      <c r="I27" t="n">
-        <v>511</v>
-      </c>
-      <c r="J27" t="n">
-        <v>34</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.07297</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.98454</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>171 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.02148</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.82384999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>245</v>
-      </c>
-      <c r="J28" t="n">
-        <v>11</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.02148</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.82385</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>1264 JUAN ANDRES VIVANCO AMORIN</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.04086</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.92928999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1517</v>
-      </c>
-      <c r="J29" t="n">
-        <v>68</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.04086</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.92929</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1517</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>0031 ROBERT F. KENNEDY</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.0235</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.93579</v>
-      </c>
-      <c r="I30" t="n">
-        <v>485</v>
-      </c>
-      <c r="J30" t="n">
-        <v>26</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.0235</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.93579</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>1239</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.03228</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.93907</v>
-      </c>
-      <c r="I31" t="n">
-        <v>628</v>
-      </c>
-      <c r="J31" t="n">
-        <v>23</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.03228</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.93907</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>183 SANTA ROSITA DE MANYLSA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.03071</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.88908000000001</v>
-      </c>
-      <c r="I32" t="n">
-        <v>367</v>
-      </c>
-      <c r="J32" t="n">
-        <v>15</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.03071</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.88908</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>1283 OKINAWA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.04551</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.89125</v>
-      </c>
-      <c r="I33" t="n">
-        <v>769</v>
-      </c>
-      <c r="J33" t="n">
-        <v>24</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.04551</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.89125</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>1136 JOHN F. KENNEDY</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.07452</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.9871</v>
-      </c>
-      <c r="I34" t="n">
-        <v>676</v>
-      </c>
-      <c r="J34" t="n">
-        <v>37</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.07452</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.9871</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>TELESFORO CATACORA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.01954</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.8845</v>
-      </c>
-      <c r="I35" t="n">
-        <v>997</v>
-      </c>
-      <c r="J35" t="n">
-        <v>46</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.01954</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.8845</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>JULIO C. TELLO</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.03461</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.94043000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1459</v>
-      </c>
-      <c r="J36" t="n">
-        <v>65</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.03461</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.94043</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1459</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>185 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.01815</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.81286</v>
-      </c>
-      <c r="I37" t="n">
-        <v>273</v>
-      </c>
-      <c r="J37" t="n">
-        <v>12</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.01815</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.81286</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>1257 REINO UNIDO DE GRAN BRETAÑA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.01972</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.82682</v>
-      </c>
-      <c r="I38" t="n">
-        <v>915</v>
-      </c>
-      <c r="J38" t="n">
-        <v>45</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.01972</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.82682</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>137 LOS LAURELES</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.02834</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.91694</v>
-      </c>
-      <c r="I39" t="n">
-        <v>250</v>
-      </c>
-      <c r="J39" t="n">
-        <v>11</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.02834</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.91694</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>COLEGIO NACIONAL VITARTE</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.02587</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.92444999999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1363</v>
-      </c>
-      <c r="J40" t="n">
-        <v>64</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.02587</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.92445</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>195 ANGELITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.02786</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.90741</v>
-      </c>
-      <c r="I41" t="n">
-        <v>277</v>
-      </c>
-      <c r="J41" t="n">
-        <v>12</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.02786</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.90741</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>0025 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.02624</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.90197000000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1861</v>
-      </c>
-      <c r="J42" t="n">
-        <v>78</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.02624</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.90197</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>046 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.025984</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-76.91823599999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1175</v>
-      </c>
-      <c r="J43" t="n">
-        <v>61</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.025984</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-76.918236</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>0026 AICHI NAGOYA</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.03073</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.90985999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1284</v>
-      </c>
-      <c r="J44" t="n">
-        <v>63</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.03073</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.90986</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.03072</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-76.88970999999999</v>
-      </c>
-      <c r="I45" t="n">
-        <v>976</v>
-      </c>
-      <c r="J45" t="n">
-        <v>41</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.03072</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.88971</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>1138 JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.0616</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-76.99594999999999</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1221</v>
-      </c>
-      <c r="J46" t="n">
-        <v>58</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.0616</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-76.99595</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>1244 MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-12.04625</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-76.92868</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1214</v>
-      </c>
-      <c r="J47" t="n">
-        <v>55</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.04625</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-76.92868</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>1231 JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.06874</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-76.97919</v>
-      </c>
-      <c r="I48" t="n">
-        <v>388</v>
-      </c>
-      <c r="J48" t="n">
-        <v>23</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.06874</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-76.97919</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>1203 DIVINO NIÑO JESUS DE MANYLSA</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.03163</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-76.88997999999999</v>
-      </c>
-      <c r="I49" t="n">
-        <v>932</v>
-      </c>
-      <c r="J49" t="n">
-        <v>31</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.03163</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-76.88998</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>1227 INDIRA GANDHI</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.03273</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-76.93170000000001</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1192</v>
-      </c>
-      <c r="J50" t="n">
-        <v>62</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.03273</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-76.9317</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>182</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.03609</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-76.90103000000001</v>
-      </c>
-      <c r="I51" t="n">
-        <v>249</v>
-      </c>
-      <c r="J51" t="n">
-        <v>10</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.03609</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-76.90103</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>168 MARIA EUGENIA MANTILLA ARIAS</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-12.0581261963589</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-76.9577655261935</v>
-      </c>
-      <c r="I52" t="n">
-        <v>324</v>
-      </c>
-      <c r="J52" t="n">
-        <v>13</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-12.0581261963589</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-76.9577655261935</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>1222 HUSARES DE JUNIN</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-12.03049</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-76.93735</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1260</v>
-      </c>
-      <c r="J53" t="n">
-        <v>48</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-12.03049</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-76.93735</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>210 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-12.04186</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-76.91925000000001</v>
-      </c>
-      <c r="I54" t="n">
-        <v>236</v>
-      </c>
-      <c r="J54" t="n">
-        <v>10</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-12.04186</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-76.91925</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>1228 LEONCIO PRADO</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-12.03599</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-76.92746</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1604</v>
-      </c>
-      <c r="J55" t="n">
-        <v>71</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-12.03599</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-76.92746</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1604</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>151</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-12.02895</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-76.92146</v>
-      </c>
-      <c r="I56" t="n">
-        <v>271</v>
-      </c>
-      <c r="J56" t="n">
-        <v>14</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-12.02895</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-76.92146</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>189 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-12.0352</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-76.93764</v>
-      </c>
-      <c r="I57" t="n">
-        <v>263</v>
-      </c>
-      <c r="J57" t="n">
-        <v>11</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-12.0352</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-76.93764</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>1212 GRUMETE MEDINA</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-12.06714</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-76.97411</v>
-      </c>
-      <c r="I58" t="n">
-        <v>512</v>
-      </c>
-      <c r="J58" t="n">
-        <v>30</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-12.06714</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-76.97411</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>0032 RAUL PORRAS BARRENECHEA</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-12.05252</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-76.95081999999999</v>
-      </c>
-      <c r="I59" t="n">
-        <v>711</v>
-      </c>
-      <c r="J59" t="n">
-        <v>38</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-12.05252</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-76.95082</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>1143 DOMINGO FAUSTINO SARMIENTO</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-12.026228</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-76.918475</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1628</v>
-      </c>
-      <c r="J60" t="n">
-        <v>58</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-12.026228</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-76.918475</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1628</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>154 LOS CLAVELES</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-12.05247</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-76.94938999999999</v>
-      </c>
-      <c r="I61" t="n">
-        <v>218</v>
-      </c>
-      <c r="J61" t="n">
-        <v>11</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-12.05247</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-76.94939</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>1209 MARISCAL TORIBIO DE LUZURIAGA</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-12.07416</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-76.97915</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1152</v>
-      </c>
-      <c r="J62" t="n">
-        <v>65</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-12.07416</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-76.97915</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>1208 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-12.06484</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-76.96853</v>
-      </c>
-      <c r="I63" t="n">
-        <v>564</v>
-      </c>
-      <c r="J63" t="n">
-        <v>28</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-12.06484</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-76.96853</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>142 GRUMETE MEDINA</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-12.06627</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-76.97233</v>
-      </c>
-      <c r="I64" t="n">
-        <v>247</v>
-      </c>
-      <c r="J64" t="n">
-        <v>12</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-12.06627</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-76.97233</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>1271</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-12.01402</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-76.81332</v>
-      </c>
-      <c r="I65" t="n">
-        <v>447</v>
-      </c>
-      <c r="J65" t="n">
-        <v>16</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-12.01402</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-76.81332</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>162 ANGELITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-12.01016</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-76.82863999999999</v>
-      </c>
-      <c r="I66" t="n">
-        <v>314</v>
-      </c>
-      <c r="J66" t="n">
-        <v>13</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-12.01016</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-76.82864</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>1260 EL AMAUTA</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-12.01836</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-76.81811999999999</v>
-      </c>
-      <c r="I67" t="n">
-        <v>1161</v>
-      </c>
-      <c r="J67" t="n">
-        <v>56</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-12.01836</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-76.81812</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1161</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>1255 WALTER PEÑALOZA RAMELLA</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-12.01948</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-76.813</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1747</v>
-      </c>
-      <c r="J68" t="n">
-        <v>79</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-12.01948</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-76.813</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1747</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>207 DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-12.01405</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-76.81328999999999</v>
-      </c>
-      <c r="I69" t="n">
-        <v>259</v>
-      </c>
-      <c r="J69" t="n">
-        <v>12</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-12.01405</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-76.81329</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>1270 JUAN EL BAUTISTA</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-12.021898</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-76.816434</v>
-      </c>
-      <c r="I70" t="n">
-        <v>693</v>
-      </c>
-      <c r="J70" t="n">
-        <v>38</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-12.021898</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-76.816434</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>6039 FERNANDO CARBAJAL SEGURA</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-12.08358</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-76.98193000000001</v>
-      </c>
-      <c r="I71" t="n">
-        <v>786</v>
-      </c>
-      <c r="J71" t="n">
-        <v>33</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-12.08358</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-76.98193</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>1285</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-12.0443</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-76.90219999999999</v>
-      </c>
-      <c r="I72" t="n">
-        <v>458</v>
-      </c>
-      <c r="J72" t="n">
-        <v>21</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-12.0443</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-76.9022</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>SANTA MARIA VIRGEN DE LA CARIDAD</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I73" t="n">
-        <v>35</v>
-      </c>
-      <c r="J73" t="n">
-        <v>8</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>FAMILIA DE NAZARETH</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-12.06052</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-76.99518999999999</v>
-      </c>
-      <c r="I74" t="n">
-        <v>70</v>
-      </c>
-      <c r="J74" t="n">
-        <v>8</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-12.06052</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-76.99519</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-12.0298</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-76.93921</v>
-      </c>
-      <c r="I75" t="n">
-        <v>577</v>
-      </c>
-      <c r="J75" t="n">
-        <v>33</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-12.0298</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-76.93921</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-12.04122</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-76.93055</v>
-      </c>
-      <c r="I76" t="n">
-        <v>262</v>
-      </c>
-      <c r="J76" t="n">
-        <v>21</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-12.04122</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-76.93055</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>SANTA ANGELA</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-12.08008</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-76.98645</v>
-      </c>
-      <c r="I77" t="n">
-        <v>770</v>
-      </c>
-      <c r="J77" t="n">
-        <v>61</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-12.08008</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-76.98645</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>ROSA VICTORIA MARTICORENA</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-12.04835</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-76.93728</v>
-      </c>
-      <c r="I78" t="n">
-        <v>203</v>
-      </c>
-      <c r="J78" t="n">
-        <v>14</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-12.04835</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-76.93728</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-12.03955</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-76.92607</v>
-      </c>
-      <c r="I79" t="n">
-        <v>586</v>
-      </c>
-      <c r="J79" t="n">
-        <v>38</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-12.03955</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-76.92607</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>PASCUAL SACO OLIVEROS - LUMBRERAS</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-12.02865</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-76.93446</v>
-      </c>
-      <c r="I80" t="n">
-        <v>331</v>
-      </c>
-      <c r="J80" t="n">
-        <v>12</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-12.02865</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-76.93446</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>ESTUDIO Y ENSEÑANZA SANTA ROSA S.C.</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-12.04061</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-76.928</v>
-      </c>
-      <c r="I81" t="n">
-        <v>398</v>
-      </c>
-      <c r="J81" t="n">
-        <v>33</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-12.04061</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-76.928</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>SANTISIMA VIRGEN DE COCHARCAS</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-12.06</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-76.99441</v>
-      </c>
-      <c r="I82" t="n">
-        <v>216</v>
-      </c>
-      <c r="J82" t="n">
-        <v>14</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-12.06</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-76.99441</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>EL PARAISO</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-12.02666</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-76.90918000000001</v>
-      </c>
-      <c r="I83" t="n">
-        <v>492</v>
-      </c>
-      <c r="J83" t="n">
-        <v>25</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-12.02666</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-76.90918</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>SAN JUAN BOSCO</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-12.02436</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-76.91658</v>
-      </c>
-      <c r="I84" t="n">
-        <v>283</v>
-      </c>
-      <c r="J84" t="n">
-        <v>16</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-12.02436</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-76.91658</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-12.06981</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-76.98188</v>
-      </c>
-      <c r="I85" t="n">
-        <v>203</v>
-      </c>
-      <c r="J85" t="n">
-        <v>8</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-12.06981</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-76.98188</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>BELEN</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-12.02992</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-76.92962</v>
-      </c>
-      <c r="I86" t="n">
-        <v>311</v>
-      </c>
-      <c r="J86" t="n">
-        <v>7</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-12.02992</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-76.92962</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>DOMINGO SAVIO</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-12.03562</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-76.92829</v>
-      </c>
-      <c r="I87" t="n">
-        <v>244</v>
-      </c>
-      <c r="J87" t="n">
-        <v>18</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-12.03562</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-76.92829</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>LA INMACULADA</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-12.03077</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-76.93765</v>
-      </c>
-      <c r="I88" t="n">
-        <v>443</v>
-      </c>
-      <c r="J88" t="n">
-        <v>25</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-12.03077</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-76.93765</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>SAN JUAN</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-12.0546</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-76.95729</v>
-      </c>
-      <c r="I89" t="n">
-        <v>311</v>
-      </c>
-      <c r="J89" t="n">
-        <v>13</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-12.0546</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-76.95729</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>MARIA DE LA ENCARNACION</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-12.07401</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-76.98563</v>
-      </c>
-      <c r="I90" t="n">
-        <v>418</v>
-      </c>
-      <c r="J90" t="n">
-        <v>48</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-12.07401</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-76.98563</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>SANTA MARIA DEL CAMINO</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-12.0725</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-76.97792</v>
-      </c>
-      <c r="I91" t="n">
-        <v>211</v>
-      </c>
-      <c r="J91" t="n">
-        <v>16</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-12.0725</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-76.97792</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-12.06389</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-76.98305999999999</v>
-      </c>
-      <c r="I92" t="n">
-        <v>83</v>
-      </c>
-      <c r="J92" t="n">
-        <v>3</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-12.06389</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-76.98306</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>JOHN DALTON</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-12.05543</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-76.94011999999999</v>
-      </c>
-      <c r="I93" t="n">
-        <v>247</v>
-      </c>
-      <c r="J93" t="n">
-        <v>19</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-12.05543</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-76.94012</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>MI UNIVERSO MAGICO</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I94" t="n">
-        <v>97</v>
-      </c>
-      <c r="J94" t="n">
-        <v>5</v>
-      </c>
-      <c r="K94" t="n">
-        <v>1</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>SANTA MARIA APOSTOL</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-12.0063</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-76.83463</v>
-      </c>
-      <c r="I95" t="n">
-        <v>226</v>
-      </c>
-      <c r="J95" t="n">
-        <v>20</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-12.0063</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-76.83463</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>SALESIAN COLLEGE</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-12.01494</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-76.82418</v>
-      </c>
-      <c r="I96" t="n">
-        <v>560</v>
-      </c>
-      <c r="J96" t="n">
-        <v>25</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-12.01494</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-76.82418</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>SANTIAGO APOSTOL</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-12.02181</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-76.88455</v>
-      </c>
-      <c r="I97" t="n">
-        <v>843</v>
-      </c>
-      <c r="J97" t="n">
-        <v>35</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-12.02181</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-76.88455</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>SANTA CATALINA</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-12.04293</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-76.91546</v>
-      </c>
-      <c r="I98" t="n">
-        <v>502</v>
-      </c>
-      <c r="J98" t="n">
-        <v>29</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-12.04293</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-76.91546</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>ALFRED NOBEL</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-12.03812</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-76.91636</v>
-      </c>
-      <c r="I99" t="n">
-        <v>959</v>
-      </c>
-      <c r="J99" t="n">
-        <v>59</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-12.03812</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-76.91636</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>ARCO IRIS</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-12.0431</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-76.93536</v>
-      </c>
-      <c r="I100" t="n">
-        <v>225</v>
-      </c>
-      <c r="J100" t="n">
-        <v>3</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-12.0431</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-76.93536</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>CORAZON DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-12.0161</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-76.824</v>
-      </c>
-      <c r="I101" t="n">
-        <v>218</v>
-      </c>
-      <c r="J101" t="n">
-        <v>6</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-12.0161</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-76.824</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>JULIO RAMON RIBEYRO</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-12.0177368366089</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-76.90025499236459</v>
-      </c>
-      <c r="I102" t="n">
-        <v>966</v>
-      </c>
-      <c r="J102" t="n">
-        <v>41</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-12.0177368366089</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-76.9002549923646</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>CRISTO SALVADOR</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-12.0786</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-76.98589</v>
-      </c>
-      <c r="I103" t="n">
-        <v>377</v>
-      </c>
-      <c r="J103" t="n">
-        <v>24</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-12.0786</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-76.98589</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5825,20 +6833,30 @@
           <t>EDUARDO PALACI</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>-12.02598</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-76.89999</v>
-      </c>
-      <c r="I104" t="n">
-        <v>408</v>
-      </c>
-      <c r="J104" t="n">
-        <v>25</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-12.02598</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-76.89999</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5877,20 +6895,30 @@
           <t>MUNDO MAGICO</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>-12.02364</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-76.9115</v>
-      </c>
-      <c r="I105" t="n">
-        <v>142</v>
-      </c>
-      <c r="J105" t="n">
-        <v>8</v>
-      </c>
-      <c r="K105" t="n">
-        <v>1</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-12.02364</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-76.9115</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5929,20 +6957,30 @@
           <t>JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>-12.06046</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-76.99576999999999</v>
-      </c>
-      <c r="I106" t="n">
-        <v>14</v>
-      </c>
-      <c r="J106" t="n">
-        <v>4</v>
-      </c>
-      <c r="K106" t="n">
-        <v>1</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-12.06046</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-76.99577</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5981,20 +7019,30 @@
           <t>JESUS MI BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G107" t="n">
-        <v>-12.05277</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-76.95299</v>
-      </c>
-      <c r="I107" t="n">
-        <v>222</v>
-      </c>
-      <c r="J107" t="n">
-        <v>11</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-12.05277</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-76.95299</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6033,20 +7081,30 @@
           <t>MARIA REINA DE LOS APOSTOLES</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>-12.0246</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-76.91198</v>
-      </c>
-      <c r="I108" t="n">
-        <v>213</v>
-      </c>
-      <c r="J108" t="n">
-        <v>30</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-12.0246</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-76.91198</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6085,20 +7143,30 @@
           <t>MARIA RAFOLS</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>-12.06258</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-76.99097</v>
-      </c>
-      <c r="I109" t="n">
-        <v>331</v>
-      </c>
-      <c r="J109" t="n">
-        <v>28</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-12.06258</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-76.99097</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6137,20 +7205,30 @@
           <t>MATER CRISTHIE</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>-12.02307</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-76.90034</v>
-      </c>
-      <c r="I110" t="n">
-        <v>240</v>
-      </c>
-      <c r="J110" t="n">
-        <v>20</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-12.02307</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-76.90034</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6189,20 +7267,30 @@
           <t>SEÑOR CAUTIVO</t>
         </is>
       </c>
-      <c r="G111" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I111" t="n">
-        <v>24</v>
-      </c>
-      <c r="J111" t="n">
-        <v>4</v>
-      </c>
-      <c r="K111" t="n">
-        <v>1</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6241,20 +7329,30 @@
           <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>-12.02141</v>
-      </c>
-      <c r="H112" t="n">
-        <v>-76.82062999999999</v>
-      </c>
-      <c r="I112" t="n">
-        <v>853</v>
-      </c>
-      <c r="J112" t="n">
-        <v>54</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-12.02141</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-76.82063</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6293,20 +7391,30 @@
           <t>LOS PORTALES DEL SABER</t>
         </is>
       </c>
-      <c r="G113" t="n">
-        <v>-12.02718</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-76.92699</v>
-      </c>
-      <c r="I113" t="n">
-        <v>221</v>
-      </c>
-      <c r="J113" t="n">
-        <v>15</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-12.02718</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-76.92699</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6345,20 +7453,30 @@
           <t>HOGAR DE JESUS</t>
         </is>
       </c>
-      <c r="G114" t="n">
-        <v>-12.06212</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-76.9971</v>
-      </c>
-      <c r="I114" t="n">
-        <v>187</v>
-      </c>
-      <c r="J114" t="n">
-        <v>13</v>
-      </c>
-      <c r="K114" t="n">
-        <v>1</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-12.06212</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-76.9971</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6397,20 +7515,30 @@
           <t>RENE DESCARTES</t>
         </is>
       </c>
-      <c r="G115" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I115" t="n">
-        <v>534</v>
-      </c>
-      <c r="J115" t="n">
-        <v>28</v>
-      </c>
-      <c r="K115" t="n">
-        <v>1</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6449,20 +7577,30 @@
           <t>FE Y ALEGRIA 53</t>
         </is>
       </c>
-      <c r="G116" t="n">
-        <v>-12.007089</v>
-      </c>
-      <c r="H116" t="n">
-        <v>-76.821257</v>
-      </c>
-      <c r="I116" t="n">
-        <v>1194</v>
-      </c>
-      <c r="J116" t="n">
-        <v>49</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-12.007089</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-76.821257</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1194</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6501,20 +7639,30 @@
           <t>SANTA ANA</t>
         </is>
       </c>
-      <c r="G117" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H117" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I117" t="n">
-        <v>142</v>
-      </c>
-      <c r="J117" t="n">
-        <v>9</v>
-      </c>
-      <c r="K117" t="n">
-        <v>1</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6553,20 +7701,30 @@
           <t>114 VIRGEN DE CHAPI</t>
         </is>
       </c>
-      <c r="G118" t="n">
-        <v>-12.06214</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-76.98819</v>
-      </c>
-      <c r="I118" t="n">
-        <v>293</v>
-      </c>
-      <c r="J118" t="n">
-        <v>17</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-12.06214</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-76.98819</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6605,20 +7763,30 @@
           <t>ALTER CHRISTUS</t>
         </is>
       </c>
-      <c r="G119" t="n">
-        <v>-12.006555</v>
-      </c>
-      <c r="H119" t="n">
-        <v>-76.844143</v>
-      </c>
-      <c r="I119" t="n">
-        <v>219</v>
-      </c>
-      <c r="J119" t="n">
-        <v>17</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-12.006555</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-76.844143</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6657,20 +7825,30 @@
           <t>BOSTON HIGH SCHOOL</t>
         </is>
       </c>
-      <c r="G120" t="n">
-        <v>-12.00886</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-76.85424999999999</v>
-      </c>
-      <c r="I120" t="n">
-        <v>255</v>
-      </c>
-      <c r="J120" t="n">
-        <v>12</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-12.00886</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-76.85425</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6709,20 +7887,30 @@
           <t>THALES DE MILETO</t>
         </is>
       </c>
-      <c r="G121" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H121" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I121" t="n">
-        <v>379</v>
-      </c>
-      <c r="J121" t="n">
-        <v>16</v>
-      </c>
-      <c r="K121" t="n">
-        <v>1</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6761,20 +7949,30 @@
           <t>MIS PASITOS</t>
         </is>
       </c>
-      <c r="G122" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H122" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I122" t="n">
-        <v>15</v>
-      </c>
-      <c r="J122" t="n">
-        <v>4</v>
-      </c>
-      <c r="K122" t="n">
-        <v>1</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6813,20 +8011,30 @@
           <t>SANTIAGO APOSTOL EL MAYOR</t>
         </is>
       </c>
-      <c r="G123" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H123" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I123" t="n">
-        <v>80</v>
-      </c>
-      <c r="J123" t="n">
-        <v>3</v>
-      </c>
-      <c r="K123" t="n">
-        <v>1</v>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -6865,20 +8073,30 @@
           <t>SACO OLIVEROS DE SALAMANCA</t>
         </is>
       </c>
-      <c r="G124" t="n">
-        <v>-12.08014</v>
-      </c>
-      <c r="H124" t="n">
-        <v>-76.98014999999999</v>
-      </c>
-      <c r="I124" t="n">
-        <v>506</v>
-      </c>
-      <c r="J124" t="n">
-        <v>25</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-12.08014</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-76.98015</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6917,20 +8135,30 @@
           <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G125" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H125" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I125" t="n">
-        <v>29</v>
-      </c>
-      <c r="J125" t="n">
-        <v>3</v>
-      </c>
-      <c r="K125" t="n">
-        <v>1</v>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -6969,20 +8197,30 @@
           <t>TECHNOLOGY SCHOOLS METROPOLITANA</t>
         </is>
       </c>
-      <c r="G126" t="n">
-        <v>-12.03317</v>
-      </c>
-      <c r="H126" t="n">
-        <v>-76.9417</v>
-      </c>
-      <c r="I126" t="n">
-        <v>381</v>
-      </c>
-      <c r="J126" t="n">
-        <v>25</v>
-      </c>
-      <c r="K126" t="n">
-        <v>1</v>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-12.03317</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-76.9417</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -7021,20 +8259,30 @@
           <t>HOWARD GARDNER</t>
         </is>
       </c>
-      <c r="G127" t="n">
-        <v>-12.02503</v>
-      </c>
-      <c r="H127" t="n">
-        <v>-76.91338</v>
-      </c>
-      <c r="I127" t="n">
-        <v>276</v>
-      </c>
-      <c r="J127" t="n">
-        <v>25</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-12.02503</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-76.91338</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -7073,20 +8321,30 @@
           <t>SAN CRISTOBAL DE MONTEROSA</t>
         </is>
       </c>
-      <c r="G128" t="n">
-        <v>-12.03601</v>
-      </c>
-      <c r="H128" t="n">
-        <v>-76.9198</v>
-      </c>
-      <c r="I128" t="n">
-        <v>205</v>
-      </c>
-      <c r="J128" t="n">
-        <v>16</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-12.03601</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-76.9198</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -7125,20 +8383,30 @@
           <t>FRANCIS SCHAEFFER</t>
         </is>
       </c>
-      <c r="G129" t="n">
-        <v>-12.02425</v>
-      </c>
-      <c r="H129" t="n">
-        <v>-76.90161000000001</v>
-      </c>
-      <c r="I129" t="n">
-        <v>295</v>
-      </c>
-      <c r="J129" t="n">
-        <v>24</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-12.02425</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-76.90161</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7177,20 +8445,30 @@
           <t>BEATITA TERESITA DE CALCUTA</t>
         </is>
       </c>
-      <c r="G130" t="n">
-        <v>-12.03662</v>
-      </c>
-      <c r="H130" t="n">
-        <v>-76.93239</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="n">
-        <v>1</v>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-12.03662</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-76.93239</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7229,20 +8507,30 @@
           <t>SANTA TERESA DE CALCUTA DE ATE</t>
         </is>
       </c>
-      <c r="G131" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H131" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I131" t="n">
-        <v>237</v>
-      </c>
-      <c r="J131" t="n">
-        <v>16</v>
-      </c>
-      <c r="K131" t="n">
-        <v>1</v>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7281,20 +8569,30 @@
           <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G132" t="n">
-        <v>-12.00948</v>
-      </c>
-      <c r="H132" t="n">
-        <v>-76.83477000000001</v>
-      </c>
-      <c r="I132" t="n">
-        <v>264</v>
-      </c>
-      <c r="J132" t="n">
-        <v>14</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-12.00948</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-76.83477</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -7333,20 +8631,30 @@
           <t>ANDINITO</t>
         </is>
       </c>
-      <c r="G133" t="n">
-        <v>-12.02098</v>
-      </c>
-      <c r="H133" t="n">
-        <v>-76.87864</v>
-      </c>
-      <c r="I133" t="n">
-        <v>217</v>
-      </c>
-      <c r="J133" t="n">
-        <v>10</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-12.02098</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-76.87864</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -7385,20 +8693,30 @@
           <t>CRUZ SACO</t>
         </is>
       </c>
-      <c r="G134" t="n">
-        <v>-12.07058</v>
-      </c>
-      <c r="H134" t="n">
-        <v>-76.97704</v>
-      </c>
-      <c r="I134" t="n">
-        <v>328</v>
-      </c>
-      <c r="J134" t="n">
-        <v>17</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-12.07058</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-76.97704</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -7437,20 +8755,30 @@
           <t>SACO OLIVEROS DE ATE</t>
         </is>
       </c>
-      <c r="G135" t="n">
-        <v>-12.05224</v>
-      </c>
-      <c r="H135" t="n">
-        <v>-76.95291</v>
-      </c>
-      <c r="I135" t="n">
-        <v>655</v>
-      </c>
-      <c r="J135" t="n">
-        <v>29</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-12.05224</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-76.95291</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -7489,20 +8817,30 @@
           <t>SANTA RITA DE ATE</t>
         </is>
       </c>
-      <c r="G136" t="n">
-        <v>-12.04023</v>
-      </c>
-      <c r="H136" t="n">
-        <v>-76.87988</v>
-      </c>
-      <c r="I136" t="n">
-        <v>220</v>
-      </c>
-      <c r="J136" t="n">
-        <v>17</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-12.04023</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-76.87988</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -7541,20 +8879,30 @@
           <t>MASTER CIENCIAS</t>
         </is>
       </c>
-      <c r="G137" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H137" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I137" t="n">
-        <v>161</v>
-      </c>
-      <c r="J137" t="n">
-        <v>22</v>
-      </c>
-      <c r="K137" t="n">
-        <v>1</v>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7593,20 +8941,30 @@
           <t>MI CRISTO SALVADOR</t>
         </is>
       </c>
-      <c r="G138" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H138" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I138" t="n">
-        <v>80</v>
-      </c>
-      <c r="J138" t="n">
-        <v>8</v>
-      </c>
-      <c r="K138" t="n">
-        <v>1</v>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7645,20 +9003,30 @@
           <t>PAMER PARACAS</t>
         </is>
       </c>
-      <c r="G139" t="n">
-        <v>-12.08035</v>
-      </c>
-      <c r="H139" t="n">
-        <v>-76.97973</v>
-      </c>
-      <c r="I139" t="n">
-        <v>337</v>
-      </c>
-      <c r="J139" t="n">
-        <v>6</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-12.08035</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-76.97973</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7697,20 +9065,30 @@
           <t>GOTITAS DE AGUA</t>
         </is>
       </c>
-      <c r="G140" t="n">
-        <v>-12.02911</v>
-      </c>
-      <c r="H140" t="n">
-        <v>-76.90164</v>
-      </c>
-      <c r="I140" t="n">
-        <v>281</v>
-      </c>
-      <c r="J140" t="n">
-        <v>15</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-12.02911</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-76.90164</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -7749,20 +9127,30 @@
           <t>MI DULCE JESUS DE PRIALE</t>
         </is>
       </c>
-      <c r="G141" t="n">
-        <v>-12.04377</v>
-      </c>
-      <c r="H141" t="n">
-        <v>-76.89163000000001</v>
-      </c>
-      <c r="I141" t="n">
-        <v>318</v>
-      </c>
-      <c r="J141" t="n">
-        <v>17</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-12.04377</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-76.89163</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -7801,20 +9189,30 @@
           <t>SACO OLIVEROS DE JAVIER PRADO</t>
         </is>
       </c>
-      <c r="G142" t="n">
-        <v>-12.03774</v>
-      </c>
-      <c r="H142" t="n">
-        <v>-76.92382000000001</v>
-      </c>
-      <c r="I142" t="n">
-        <v>347</v>
-      </c>
-      <c r="J142" t="n">
-        <v>14</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0</v>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-12.03774</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-76.92382</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -7853,20 +9251,30 @@
           <t>LAS GARDENIAS</t>
         </is>
       </c>
-      <c r="G143" t="n">
-        <v>-12.01465</v>
-      </c>
-      <c r="H143" t="n">
-        <v>-76.87034</v>
-      </c>
-      <c r="I143" t="n">
-        <v>213</v>
-      </c>
-      <c r="J143" t="n">
-        <v>9</v>
-      </c>
-      <c r="K143" t="n">
-        <v>0</v>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-12.01465</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-76.87034</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -7905,20 +9313,30 @@
           <t>SIN FRONTERAS</t>
         </is>
       </c>
-      <c r="G144" t="n">
-        <v>-12.01382</v>
-      </c>
-      <c r="H144" t="n">
-        <v>-76.87969</v>
-      </c>
-      <c r="I144" t="n">
-        <v>224</v>
-      </c>
-      <c r="J144" t="n">
-        <v>3</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0</v>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-12.01382</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-76.87969</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -7957,20 +9375,30 @@
           <t>INTERNACIONAL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="G145" t="n">
-        <v>-12.01211</v>
-      </c>
-      <c r="H145" t="n">
-        <v>-76.85382</v>
-      </c>
-      <c r="I145" t="n">
-        <v>332</v>
-      </c>
-      <c r="J145" t="n">
-        <v>20</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0</v>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-12.01211</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-76.85382</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -8009,20 +9437,30 @@
           <t>ANDINO</t>
         </is>
       </c>
-      <c r="G146" t="n">
-        <v>-12.020981</v>
-      </c>
-      <c r="H146" t="n">
-        <v>-76.87848700000001</v>
-      </c>
-      <c r="I146" t="n">
-        <v>330</v>
-      </c>
-      <c r="J146" t="n">
-        <v>16</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0</v>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-12.020981</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-76.878487</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -8061,20 +9499,30 @@
           <t>SACO OLIVEROS</t>
         </is>
       </c>
-      <c r="G147" t="n">
-        <v>-12.05391</v>
-      </c>
-      <c r="H147" t="n">
-        <v>-76.96043</v>
-      </c>
-      <c r="I147" t="n">
-        <v>270</v>
-      </c>
-      <c r="J147" t="n">
-        <v>17</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0</v>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-12.05391</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-76.96043</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -8113,20 +9561,30 @@
           <t>CIENCIAS APLICADAS ALBERT EINSTEIN</t>
         </is>
       </c>
-      <c r="G148" t="n">
-        <v>-12.011</v>
-      </c>
-      <c r="H148" t="n">
-        <v>-76.82285</v>
-      </c>
-      <c r="I148" t="n">
-        <v>273</v>
-      </c>
-      <c r="J148" t="n">
-        <v>16</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0</v>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-12.011</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-76.82285</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -8165,20 +9623,30 @@
           <t>UNIMASTER</t>
         </is>
       </c>
-      <c r="G149" t="n">
-        <v>-12.02784</v>
-      </c>
-      <c r="H149" t="n">
-        <v>-76.93015</v>
-      </c>
-      <c r="I149" t="n">
-        <v>233</v>
-      </c>
-      <c r="J149" t="n">
-        <v>17</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0</v>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-12.02784</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-76.93015</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -8217,20 +9685,30 @@
           <t>SACO OLIVEROS APEIRON</t>
         </is>
       </c>
-      <c r="G150" t="n">
-        <v>-12.05513</v>
-      </c>
-      <c r="H150" t="n">
-        <v>-76.95376</v>
-      </c>
-      <c r="I150" t="n">
-        <v>548</v>
-      </c>
-      <c r="J150" t="n">
-        <v>23</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0</v>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-12.05513</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-76.95376</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -8269,20 +9747,30 @@
           <t>MAHATMA GANDHI</t>
         </is>
       </c>
-      <c r="G151" t="n">
-        <v>-12.0274</v>
-      </c>
-      <c r="H151" t="n">
-        <v>-76.90405</v>
-      </c>
-      <c r="I151" t="n">
-        <v>272</v>
-      </c>
-      <c r="J151" t="n">
-        <v>18</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-12.0274</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-76.90405</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -8321,20 +9809,30 @@
           <t>1236 ALFONSO BARRANTES LINGAN</t>
         </is>
       </c>
-      <c r="G152" t="n">
-        <v>-12.00963</v>
-      </c>
-      <c r="H152" t="n">
-        <v>-76.82848</v>
-      </c>
-      <c r="I152" t="n">
-        <v>1452</v>
-      </c>
-      <c r="J152" t="n">
-        <v>63</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0</v>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-12.00963</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-76.82848</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -8373,20 +9871,30 @@
           <t>SALESIAN INNOVA</t>
         </is>
       </c>
-      <c r="G153" t="n">
-        <v>-12.062</v>
-      </c>
-      <c r="H153" t="n">
-        <v>-76.99515</v>
-      </c>
-      <c r="I153" t="n">
-        <v>76</v>
-      </c>
-      <c r="J153" t="n">
-        <v>7</v>
-      </c>
-      <c r="K153" t="n">
-        <v>1</v>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-12.062</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-76.99515</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -8425,20 +9933,30 @@
           <t>MARTIR DE LA MEDICINA DANIEL A. CARRION</t>
         </is>
       </c>
-      <c r="G154" t="n">
-        <v>-12.00681</v>
-      </c>
-      <c r="H154" t="n">
-        <v>-76.84448999999999</v>
-      </c>
-      <c r="I154" t="n">
-        <v>259</v>
-      </c>
-      <c r="J154" t="n">
-        <v>15</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0</v>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-12.00681</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-76.84449</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -8477,20 +9995,30 @@
           <t>LAS AMERICAS DE ATE</t>
         </is>
       </c>
-      <c r="G155" t="n">
-        <v>-12.03475</v>
-      </c>
-      <c r="H155" t="n">
-        <v>-76.90406</v>
-      </c>
-      <c r="I155" t="n">
-        <v>335</v>
-      </c>
-      <c r="J155" t="n">
-        <v>14</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0</v>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-12.03475</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-76.90406</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -8529,20 +10057,30 @@
           <t>AKIRA KATO</t>
         </is>
       </c>
-      <c r="G156" t="n">
-        <v>-12.023037</v>
-      </c>
-      <c r="H156" t="n">
-        <v>-76.837182</v>
-      </c>
-      <c r="I156" t="n">
-        <v>693</v>
-      </c>
-      <c r="J156" t="n">
-        <v>33</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0</v>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-12.023037</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-76.837182</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -8581,20 +10119,30 @@
           <t>1288 ALBERT EINSTEIN</t>
         </is>
       </c>
-      <c r="G157" t="n">
-        <v>-12.02704</v>
-      </c>
-      <c r="H157" t="n">
-        <v>-76.95171000000001</v>
-      </c>
-      <c r="I157" t="n">
-        <v>664</v>
-      </c>
-      <c r="J157" t="n">
-        <v>25</v>
-      </c>
-      <c r="K157" t="n">
-        <v>0</v>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-12.02704</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-76.95171</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -8633,20 +10181,30 @@
           <t>1289</t>
         </is>
       </c>
-      <c r="G158" t="n">
-        <v>-12.03705</v>
-      </c>
-      <c r="H158" t="n">
-        <v>-76.82411</v>
-      </c>
-      <c r="I158" t="n">
-        <v>338</v>
-      </c>
-      <c r="J158" t="n">
-        <v>18</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0</v>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-12.03705</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-76.82411</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -8685,20 +10243,30 @@
           <t>TRILCE DE SALAMANCA</t>
         </is>
       </c>
-      <c r="G159" t="n">
-        <v>-12.08007</v>
-      </c>
-      <c r="H159" t="n">
-        <v>-76.98502999999999</v>
-      </c>
-      <c r="I159" t="n">
-        <v>271</v>
-      </c>
-      <c r="J159" t="n">
-        <v>13</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0</v>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-12.08007</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-76.98503</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -8737,20 +10305,30 @@
           <t>SANTA INES</t>
         </is>
       </c>
-      <c r="G160" t="n">
-        <v>-12.00572</v>
-      </c>
-      <c r="H160" t="n">
-        <v>-76.83351</v>
-      </c>
-      <c r="I160" t="n">
-        <v>504</v>
-      </c>
-      <c r="J160" t="n">
-        <v>24</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0</v>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-12.00572</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-76.83351</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -8789,20 +10367,30 @@
           <t>SELECCION A DE ATE</t>
         </is>
       </c>
-      <c r="G161" t="n">
-        <v>-12.0281</v>
-      </c>
-      <c r="H161" t="n">
-        <v>-76.93807</v>
-      </c>
-      <c r="I161" t="n">
-        <v>316</v>
-      </c>
-      <c r="J161" t="n">
-        <v>11</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0</v>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-12.0281</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-76.93807</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -8841,20 +10429,30 @@
           <t>CIBERT UNI DE ATE VITARTE</t>
         </is>
       </c>
-      <c r="G162" t="n">
-        <v>-12.03263</v>
-      </c>
-      <c r="H162" t="n">
-        <v>-76.93733</v>
-      </c>
-      <c r="I162" t="n">
-        <v>759</v>
-      </c>
-      <c r="J162" t="n">
-        <v>28</v>
-      </c>
-      <c r="K162" t="n">
-        <v>0</v>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-12.03263</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-76.93733</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -8893,20 +10491,30 @@
           <t>SAN IGNACIO SCHOOL</t>
         </is>
       </c>
-      <c r="G163" t="n">
-        <v>-12.030403</v>
-      </c>
-      <c r="H163" t="n">
-        <v>-76.935874</v>
-      </c>
-      <c r="I163" t="n">
-        <v>429</v>
-      </c>
-      <c r="J163" t="n">
-        <v>20</v>
-      </c>
-      <c r="K163" t="n">
-        <v>0</v>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-12.030403</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-76.935874</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -8945,20 +10553,30 @@
           <t>1290 NUEVA AMERICA</t>
         </is>
       </c>
-      <c r="G164" t="n">
-        <v>-12.039784</v>
-      </c>
-      <c r="H164" t="n">
-        <v>-76.89204599999999</v>
-      </c>
-      <c r="I164" t="n">
-        <v>946</v>
-      </c>
-      <c r="J164" t="n">
-        <v>39</v>
-      </c>
-      <c r="K164" t="n">
-        <v>0</v>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-12.039784</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-76.892046</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -8997,20 +10615,30 @@
           <t>SANTA MARIA INTERNATIONAL SCHOOL</t>
         </is>
       </c>
-      <c r="G165" t="n">
-        <v>-12.03895</v>
-      </c>
-      <c r="H165" t="n">
-        <v>-76.93109</v>
-      </c>
-      <c r="I165" t="n">
-        <v>769</v>
-      </c>
-      <c r="J165" t="n">
-        <v>26</v>
-      </c>
-      <c r="K165" t="n">
-        <v>0</v>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-12.03895</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-76.93109</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -9049,20 +10677,30 @@
           <t>LUCERITO DE AMOR</t>
         </is>
       </c>
-      <c r="G166" t="n">
-        <v>-12.01838</v>
-      </c>
-      <c r="H166" t="n">
-        <v>-76.88581000000001</v>
-      </c>
-      <c r="I166" t="n">
-        <v>202</v>
-      </c>
-      <c r="J166" t="n">
-        <v>14</v>
-      </c>
-      <c r="K166" t="n">
-        <v>0</v>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-12.01838</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-76.88581</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -9101,20 +10739,30 @@
           <t>PACIFICO</t>
         </is>
       </c>
-      <c r="G167" t="n">
-        <v>-12.03653</v>
-      </c>
-      <c r="H167" t="n">
-        <v>-76.92355999999999</v>
-      </c>
-      <c r="I167" t="n">
-        <v>347</v>
-      </c>
-      <c r="J167" t="n">
-        <v>58</v>
-      </c>
-      <c r="K167" t="n">
-        <v>0</v>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-12.03653</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-76.92356</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -9153,20 +10801,30 @@
           <t>ROMEO LUNA VICTORIA</t>
         </is>
       </c>
-      <c r="G168" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H168" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I168" t="n">
-        <v>140</v>
-      </c>
-      <c r="J168" t="n">
-        <v>9</v>
-      </c>
-      <c r="K168" t="n">
-        <v>1</v>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -9205,20 +10863,30 @@
           <t>ENRIQUE PESTALOZZI</t>
         </is>
       </c>
-      <c r="G169" t="n">
-        <v>-12.01076</v>
-      </c>
-      <c r="H169" t="n">
-        <v>-76.85363</v>
-      </c>
-      <c r="I169" t="n">
-        <v>202</v>
-      </c>
-      <c r="J169" t="n">
-        <v>6</v>
-      </c>
-      <c r="K169" t="n">
-        <v>0</v>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-12.01076</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-76.85363</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -9257,20 +10925,30 @@
           <t>LA CATOLICA REDEMPTORIS MATER</t>
         </is>
       </c>
-      <c r="G170" t="n">
-        <v>-12.03121</v>
-      </c>
-      <c r="H170" t="n">
-        <v>-76.88959</v>
-      </c>
-      <c r="I170" t="n">
-        <v>247</v>
-      </c>
-      <c r="J170" t="n">
-        <v>14</v>
-      </c>
-      <c r="K170" t="n">
-        <v>0</v>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-12.03121</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-76.88959</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -9309,20 +10987,30 @@
           <t>NUESTRA SEÑORA DE LA CRUZ</t>
         </is>
       </c>
-      <c r="G171" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H171" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I171" t="n">
-        <v>25</v>
-      </c>
-      <c r="J171" t="n">
-        <v>1</v>
-      </c>
-      <c r="K171" t="n">
-        <v>1</v>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -9361,20 +11049,30 @@
           <t>INNOVA SCHOOLS - PURUCHUCO</t>
         </is>
       </c>
-      <c r="G172" t="n">
-        <v>-12.0429</v>
-      </c>
-      <c r="H172" t="n">
-        <v>-76.93304000000001</v>
-      </c>
-      <c r="I172" t="n">
-        <v>1051</v>
-      </c>
-      <c r="J172" t="n">
-        <v>48</v>
-      </c>
-      <c r="K172" t="n">
-        <v>0</v>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-12.0429</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-76.93304</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -9413,20 +11111,30 @@
           <t>INNOVA SCHOOLS - VITARTE</t>
         </is>
       </c>
-      <c r="G173" t="n">
-        <v>-12.02798</v>
-      </c>
-      <c r="H173" t="n">
-        <v>-76.93862</v>
-      </c>
-      <c r="I173" t="n">
-        <v>1055</v>
-      </c>
-      <c r="J173" t="n">
-        <v>58</v>
-      </c>
-      <c r="K173" t="n">
-        <v>0</v>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-12.02798</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-76.93862</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -9465,20 +11173,30 @@
           <t>SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G174" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H174" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I174" t="n">
-        <v>386</v>
-      </c>
-      <c r="J174" t="n">
-        <v>17</v>
-      </c>
-      <c r="K174" t="n">
-        <v>1</v>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -9517,20 +11235,30 @@
           <t>MIS PEQUEÑOS GENIOS</t>
         </is>
       </c>
-      <c r="G175" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H175" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I175" t="n">
-        <v>4</v>
-      </c>
-      <c r="J175" t="n">
-        <v>2</v>
-      </c>
-      <c r="K175" t="n">
-        <v>1</v>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -9569,20 +11297,30 @@
           <t>TARPUY MODERNO</t>
         </is>
       </c>
-      <c r="G176" t="n">
-        <v>-12.01185</v>
-      </c>
-      <c r="H176" t="n">
-        <v>-76.85059</v>
-      </c>
-      <c r="I176" t="n">
-        <v>312</v>
-      </c>
-      <c r="J176" t="n">
-        <v>14</v>
-      </c>
-      <c r="K176" t="n">
-        <v>0</v>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-12.01185</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-76.85059</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -9621,20 +11359,30 @@
           <t>VILLA PROGRESO</t>
         </is>
       </c>
-      <c r="G177" t="n">
-        <v>-12.00744</v>
-      </c>
-      <c r="H177" t="n">
-        <v>-76.833</v>
-      </c>
-      <c r="I177" t="n">
-        <v>489</v>
-      </c>
-      <c r="J177" t="n">
-        <v>28</v>
-      </c>
-      <c r="K177" t="n">
-        <v>0</v>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-12.00744</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-76.833</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -9673,20 +11421,30 @@
           <t>TRILCE DE SALAMANCA</t>
         </is>
       </c>
-      <c r="G178" t="n">
-        <v>-12.07899</v>
-      </c>
-      <c r="H178" t="n">
-        <v>-76.98265000000001</v>
-      </c>
-      <c r="I178" t="n">
-        <v>307</v>
-      </c>
-      <c r="J178" t="n">
-        <v>22</v>
-      </c>
-      <c r="K178" t="n">
-        <v>0</v>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-12.07899</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-76.98265</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -9725,20 +11483,30 @@
           <t>MUNDO KIDS</t>
         </is>
       </c>
-      <c r="G179" t="n">
-        <v>-12.027489</v>
-      </c>
-      <c r="H179" t="n">
-        <v>-76.94935099999999</v>
-      </c>
-      <c r="I179" t="n">
-        <v>43</v>
-      </c>
-      <c r="J179" t="n">
-        <v>3</v>
-      </c>
-      <c r="K179" t="n">
-        <v>2</v>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-12.027489</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-76.949351</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -9777,20 +11545,30 @@
           <t>SANTA LUISA DE MARILLAC II</t>
         </is>
       </c>
-      <c r="G180" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H180" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I180" t="n">
-        <v>295</v>
-      </c>
-      <c r="J180" t="n">
-        <v>4</v>
-      </c>
-      <c r="K180" t="n">
-        <v>1</v>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -9829,20 +11607,30 @@
           <t>CIBERT UNI DE VITARTE</t>
         </is>
       </c>
-      <c r="G181" t="n">
-        <v>-12.03265</v>
-      </c>
-      <c r="H181" t="n">
-        <v>-76.93744</v>
-      </c>
-      <c r="I181" t="n">
-        <v>56</v>
-      </c>
-      <c r="J181" t="n">
-        <v>2</v>
-      </c>
-      <c r="K181" t="n">
-        <v>1</v>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-12.03265</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-76.93744</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -9881,20 +11669,30 @@
           <t>CIBERT VITARTE</t>
         </is>
       </c>
-      <c r="G182" t="n">
-        <v>-12.031046</v>
-      </c>
-      <c r="H182" t="n">
-        <v>-76.92443299999999</v>
-      </c>
-      <c r="I182" t="n">
-        <v>749</v>
-      </c>
-      <c r="J182" t="n">
-        <v>28</v>
-      </c>
-      <c r="K182" t="n">
-        <v>0</v>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-12.031046</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-76.924433</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -9933,20 +11731,30 @@
           <t>VILLA MARGARITA</t>
         </is>
       </c>
-      <c r="G183" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H183" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I183" t="n">
-        <v>25</v>
-      </c>
-      <c r="J183" t="n">
-        <v>1</v>
-      </c>
-      <c r="K183" t="n">
-        <v>1</v>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -9985,20 +11793,30 @@
           <t>MI MUNDO MAGICO REAL FELIPE</t>
         </is>
       </c>
-      <c r="G184" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H184" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I184" t="n">
-        <v>39</v>
-      </c>
-      <c r="J184" t="n">
-        <v>5</v>
-      </c>
-      <c r="K184" t="n">
-        <v>1</v>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -10037,20 +11855,30 @@
           <t>THALES DE SANTA CLARA</t>
         </is>
       </c>
-      <c r="G185" t="n">
-        <v>-12.01337</v>
-      </c>
-      <c r="H185" t="n">
-        <v>-76.87966</v>
-      </c>
-      <c r="I185" t="n">
-        <v>233</v>
-      </c>
-      <c r="J185" t="n">
-        <v>27</v>
-      </c>
-      <c r="K185" t="n">
-        <v>0</v>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-12.01337</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-76.87966</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -10089,20 +11917,30 @@
           <t>INNOVA SCHOOLS - ATE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G186" t="n">
-        <v>-12.02748</v>
-      </c>
-      <c r="H186" t="n">
-        <v>-76.88939000000001</v>
-      </c>
-      <c r="I186" t="n">
-        <v>722</v>
-      </c>
-      <c r="J186" t="n">
-        <v>43</v>
-      </c>
-      <c r="K186" t="n">
-        <v>0</v>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-12.02748</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-76.88939</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -10141,20 +11979,30 @@
           <t>THALES DE VITARTE</t>
         </is>
       </c>
-      <c r="G187" t="n">
-        <v>-12.02601</v>
-      </c>
-      <c r="H187" t="n">
-        <v>-76.90835</v>
-      </c>
-      <c r="I187" t="n">
-        <v>497</v>
-      </c>
-      <c r="J187" t="n">
-        <v>38</v>
-      </c>
-      <c r="K187" t="n">
-        <v>1</v>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-12.02601</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-76.90835</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -10193,20 +12041,30 @@
           <t>INNOVA SCHOOLS - ATE MAYORAZGO</t>
         </is>
       </c>
-      <c r="G188" t="n">
-        <v>-12.0432</v>
-      </c>
-      <c r="H188" t="n">
-        <v>-76.93304999999999</v>
-      </c>
-      <c r="I188" t="n">
-        <v>1059</v>
-      </c>
-      <c r="J188" t="n">
-        <v>50</v>
-      </c>
-      <c r="K188" t="n">
-        <v>0</v>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-12.0432</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-76.93305</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -10245,20 +12103,30 @@
           <t>KAROL WOJTYLA</t>
         </is>
       </c>
-      <c r="G189" t="n">
-        <v>-12.00694</v>
-      </c>
-      <c r="H189" t="n">
-        <v>-76.84385</v>
-      </c>
-      <c r="I189" t="n">
-        <v>299</v>
-      </c>
-      <c r="J189" t="n">
-        <v>17</v>
-      </c>
-      <c r="K189" t="n">
-        <v>0</v>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-12.00694</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-76.84385</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -10297,20 +12165,30 @@
           <t>MARIA DE LAS MERCEDES DE SALAMANCA</t>
         </is>
       </c>
-      <c r="G190" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H190" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I190" t="n">
-        <v>88</v>
-      </c>
-      <c r="J190" t="n">
-        <v>2</v>
-      </c>
-      <c r="K190" t="n">
-        <v>1</v>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -10349,20 +12227,30 @@
           <t>SALESIAN INNOVA SCHOOL</t>
         </is>
       </c>
-      <c r="G191" t="n">
-        <v>-12.014989</v>
-      </c>
-      <c r="H191" t="n">
-        <v>-76.83885600000001</v>
-      </c>
-      <c r="I191" t="n">
-        <v>228</v>
-      </c>
-      <c r="J191" t="n">
-        <v>11</v>
-      </c>
-      <c r="K191" t="n">
-        <v>1</v>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-12.014989</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-76.838856</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -10401,20 +12289,30 @@
           <t>THALES</t>
         </is>
       </c>
-      <c r="G192" t="n">
-        <v>-12.01347</v>
-      </c>
-      <c r="H192" t="n">
-        <v>-76.821473</v>
-      </c>
-      <c r="I192" t="n">
-        <v>439</v>
-      </c>
-      <c r="J192" t="n">
-        <v>63</v>
-      </c>
-      <c r="K192" t="n">
-        <v>0</v>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-12.01347</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-76.821473</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -10453,20 +12351,30 @@
           <t>TESORITOS DE DIOS</t>
         </is>
       </c>
-      <c r="G193" t="n">
-        <v>-12.025933</v>
-      </c>
-      <c r="H193" t="n">
-        <v>-76.918729</v>
-      </c>
-      <c r="I193" t="n">
-        <v>78</v>
-      </c>
-      <c r="J193" t="n">
-        <v>6</v>
-      </c>
-      <c r="K193" t="n">
-        <v>1</v>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-12.025933</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-76.918729</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>291551</t>
+          <t>565536</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>164 JEAN PIAGET</t>
+          <t>BEATITA TERESITA DE CALCUTA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.01357</t>
+          <t>-12.03662</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.83749</t>
+          <t>-76.93239</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>291565</t>
+          <t>722254</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1252 SANTA ISABEL</t>
+          <t>NUESTRA SEÑORA DE LA CRUZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.03596</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.90168</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>291570</t>
+          <t>827524</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1281 SANTA MARIA</t>
+          <t>VILLA MARGARITA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.04287</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.92451</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>291594</t>
+          <t>292386</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1249 JAVIER HERAUD</t>
+          <t>182</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.02791</t>
+          <t>-12.03609</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.91514</t>
+          <t>-76.90103</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>291607</t>
+          <t>292414</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1237 JORGE D. GILES LLANOS</t>
+          <t>210 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.01951</t>
+          <t>-12.04186</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.83795</t>
+          <t>-76.91925</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>291612</t>
+          <t>617093</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1263 PURUCHUCO</t>
+          <t>ANDINITO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.04869</t>
+          <t>-12.02098</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.93006</t>
+          <t>-76.87864</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>291626</t>
+          <t>291570</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>1281 SANTA MARIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.04295</t>
+          <t>-12.04287</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.8978</t>
+          <t>-76.92451</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>301</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>291631</t>
+          <t>291971</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1262 EL AMAUTA JOSE C. MARIATEGUI</t>
+          <t>171 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.04274</t>
+          <t>-12.02148</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.89804</t>
+          <t>-76.82385</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>291645</t>
+          <t>292145</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>137 LOS LAURELES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.04497</t>
+          <t>-12.02834</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.91523</t>
+          <t>-76.91694</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>291650</t>
+          <t>292447</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>192 SANTA ROSITA DE LIMA</t>
+          <t>189 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.04855</t>
+          <t>-12.0352</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.92995</t>
+          <t>-76.93764</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>291688</t>
+          <t>292485</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154 LOS CLAVELES</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.02871</t>
+          <t>-12.05247</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.92471</t>
+          <t>-76.94939</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>291706</t>
+          <t>294489</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0029 MARCO PUENTE LLANOS</t>
+          <t>JESUS MI BUEN PASTOR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.0312</t>
+          <t>-12.05277</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.92155</t>
+          <t>-76.95299</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>291711</t>
+          <t>721283</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>COLEGIO NACIONAL MIXTO HUAYCAN</t>
+          <t>SELECCION A DE ATE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.01531</t>
+          <t>-12.0281</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.82682</t>
+          <t>-76.93807</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>316</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>291725</t>
+          <t>854720</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1215 SAN JUAN PARIACHI</t>
+          <t>SALESIAN INNOVA SCHOOL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.01066</t>
+          <t>-12.014989</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.8694</t>
+          <t>-76.838856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>228</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>291730</t>
+          <t>291688</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>500 EL BOSQUE</t>
+          <t>134</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.06206</t>
+          <t>-12.02871</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.98335</t>
+          <t>-76.92471</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>337</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>291768</t>
+          <t>292112</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0074 FERNANDO BELAUNDE TERRY</t>
+          <t>185 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.07036</t>
+          <t>-12.01815</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.98429</t>
+          <t>-76.81286</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>291787</t>
+          <t>292169</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1258 SEBASTIAN LORENTE</t>
+          <t>195 ANGELITOS DE JESUS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.01452</t>
+          <t>-12.02786</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.82606</t>
+          <t>-76.90741</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>291810</t>
+          <t>292522</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1243 SAN ROQUE</t>
+          <t>142 GRUMETE MEDINA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.02021</t>
+          <t>-12.06627</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.90614</t>
+          <t>-76.97233</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>291829</t>
+          <t>292602</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>135 NIÑO JESUS</t>
+          <t>207 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.0733</t>
+          <t>-12.01405</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.98087</t>
+          <t>-76.81329</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>291834</t>
+          <t>293041</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>PASCUAL SACO OLIVEROS - LUMBRERAS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.02864</t>
+          <t>-12.02865</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.92962</t>
+          <t>-76.93446</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>291848</t>
+          <t>506245</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1251 PERUANO SUIZO</t>
+          <t>BOSTON HIGH SCHOOL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.02194</t>
+          <t>-12.00886</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.8717</t>
+          <t>-76.85425</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>291867</t>
+          <t>291551</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1245 JOSE CARLOS MARIATEGUI</t>
+          <t>164 JEAN PIAGET</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.01519</t>
+          <t>-12.01357</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.82089</t>
+          <t>-76.83749</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>291914</t>
+          <t>291626</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1229 CAP. JULIO A. PONCE ANTUNEZ DE MAYOLO</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.05782</t>
+          <t>-12.04295</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.95716</t>
+          <t>-76.8978</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>291933</t>
+          <t>291730</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1265 SANTA ROSA DE LIMA</t>
+          <t>500 EL BOSQUE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.00932</t>
+          <t>-12.06206</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.816</t>
+          <t>-76.98335</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>291947</t>
+          <t>291810</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1243 SAN ROQUE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.03692</t>
+          <t>-12.02021</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.93268</t>
+          <t>-76.90614</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>276</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>291952</t>
+          <t>291933</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA ESPERANZA</t>
+          <t>1265 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.07297</t>
+          <t>-12.00932</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.98454</t>
+          <t>-76.816</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>291971</t>
+          <t>292391</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>171 VIRGEN DEL CARMEN</t>
+          <t>168 MARIA EUGENIA MANTILLA ARIAS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.02148</t>
+          <t>-12.0581261963589</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.82385</t>
+          <t>-76.9577655261935</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>291985</t>
+          <t>292555</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1264 JUAN ANDRES VIVANCO AMORIN</t>
+          <t>162 ANGELITOS DE JESUS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.04086</t>
+          <t>-12.01016</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.92929</t>
+          <t>-76.82864</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>314</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>291990</t>
+          <t>293630</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0031 ROBERT F. KENNEDY</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.0235</t>
+          <t>-12.0546</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.93579</t>
+          <t>-76.95729</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>311</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>292008</t>
+          <t>294861</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>HOGAR DE JESUS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.03228</t>
+          <t>-12.06212</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.93907</t>
+          <t>-76.9971</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>187</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>292051</t>
+          <t>720981</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>183 SANTA ROSITA DE MANYLSA</t>
+          <t>TRILCE DE SALAMANCA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.03071</t>
+          <t>-12.08007</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.88908</t>
+          <t>-76.98503</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>292065</t>
+          <t>291645</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1283 OKINAWA</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.04551</t>
+          <t>-12.04497</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.89125</t>
+          <t>-76.91523</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>292070</t>
+          <t>291829</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1136 JOHN F. KENNEDY</t>
+          <t>135 NIÑO JESUS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.07452</t>
+          <t>-12.0733</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.9871</t>
+          <t>-76.98087</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>292089</t>
+          <t>292433</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TELESFORO CATACORA</t>
+          <t>151</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.01954</t>
+          <t>-12.02895</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.8845</t>
+          <t>-76.92146</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>292094</t>
+          <t>293022</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JULIO C. TELLO</t>
+          <t>ROSA VICTORIA MARTICORENA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.03461</t>
+          <t>-12.04835</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.94043</t>
+          <t>-76.93728</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>292112</t>
+          <t>293140</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>185 SEÑOR DE LOS MILAGROS</t>
+          <t>SANTISIMA VIRGEN DE COCHARCAS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.01815</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.81286</t>
+          <t>-76.99441</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>292131</t>
+          <t>615193</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1257 REINO UNIDO DE GRAN BRETAÑA</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.01972</t>
+          <t>-12.00948</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.82682</t>
+          <t>-76.83477</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>292145</t>
+          <t>655198</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>137 LOS LAURELES</t>
+          <t>SACO OLIVEROS DE JAVIER PRADO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.02834</t>
+          <t>-12.03774</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.91694</t>
+          <t>-76.92382</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>347</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>292150</t>
+          <t>720373</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>COLEGIO NACIONAL VITARTE</t>
+          <t>LAS AMERICAS DE ATE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.02587</t>
+          <t>-12.03475</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.92445</t>
+          <t>-76.90406</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>292169</t>
+          <t>721805</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>195 ANGELITOS DE JESUS</t>
+          <t>LUCERITO DE AMOR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.02786</t>
+          <t>-12.01838</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.90741</t>
+          <t>-76.88581</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>292188</t>
+          <t>722145</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0025 SAN MARTIN DE PORRES</t>
+          <t>LA CATOLICA REDEMPTORIS MATER</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.02624</t>
+          <t>-12.03121</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.90197</t>
+          <t>-76.88959</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>292254</t>
+          <t>755027</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>046 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>TARPUY MODERNO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.025984</t>
+          <t>-12.01185</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.918236</t>
+          <t>-76.85059</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>292273</t>
+          <t>291594</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0026 AICHI NAGOYA</t>
+          <t>1249 JAVIER HERAUD</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.03073</t>
+          <t>-12.02791</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.90986</t>
+          <t>-76.91514</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>292305</t>
+          <t>292051</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>183 SANTA ROSITA DE MANYLSA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.03072</t>
+          <t>-12.03071</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.88971</t>
+          <t>-76.88908</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,42 +3229,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>292310</t>
+          <t>294682</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1138 JOSE ABELARDO QUIÑONES</t>
+          <t>LOS PORTALES DEL SABER</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.0616</t>
+          <t>-12.02718</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.99595</t>
+          <t>-76.92699</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>292329</t>
+          <t>651402</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1244 MICAELA BASTIDAS</t>
+          <t>GOTITAS DE AGUA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.04625</t>
+          <t>-12.02911</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.92868</t>
+          <t>-76.90164</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>281</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>292348</t>
+          <t>720349</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1231 JOSE LUIS BUSTAMANTE Y RIVERO</t>
+          <t>MARTIR DE LA MEDICINA DANIEL A. CARRION</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.06874</t>
+          <t>-12.00681</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.97919</t>
+          <t>-76.84449</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>292353</t>
+          <t>292541</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1203 DIVINO NIÑO JESUS DE MANYLSA</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.03163</t>
+          <t>-12.01402</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.88998</t>
+          <t>-76.81332</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>447</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>292367</t>
+          <t>293244</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1227 INDIRA GANDHI</t>
+          <t>SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.03273</t>
+          <t>-12.02436</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.9317</t>
+          <t>-76.91658</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>283</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>292386</t>
+          <t>293734</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>SANTA MARIA DEL CAMINO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.03609</t>
+          <t>-12.0725</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.90103</t>
+          <t>-76.97792</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,42 +3601,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>292391</t>
+          <t>523971</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>168 MARIA EUGENIA MANTILLA ARIAS</t>
+          <t>THALES DE MILETO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.0581261963589</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.9577655261935</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>379</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>292409</t>
+          <t>554986</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1222 HUSARES DE JUNIN</t>
+          <t>SAN CRISTOBAL DE MONTEROSA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.03049</t>
+          <t>-12.03601</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.93735</t>
+          <t>-76.9198</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>292414</t>
+          <t>592592</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>210 MARIA PARADO DE BELLIDO</t>
+          <t>SANTA TERESA DE CALCUTA DE ATE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.04186</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.91925</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>292428</t>
+          <t>718515</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1228 LEONCIO PRADO</t>
+          <t>ANDINO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.03599</t>
+          <t>-12.020981</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.92746</t>
+          <t>-76.878487</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>292433</t>
+          <t>719807</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>CIENCIAS APLICADAS ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.02895</t>
+          <t>-12.011</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.92146</t>
+          <t>-76.82285</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>292447</t>
+          <t>304902</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>189 SAGRADO CORAZON DE JESUS</t>
+          <t>114 VIRGEN DE CHAPI</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.0352</t>
+          <t>-12.06214</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-76.93764</t>
+          <t>-76.98819</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>292452</t>
+          <t>314656</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1212 GRUMETE MEDINA</t>
+          <t>ALTER CHRISTUS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.06714</t>
+          <t>-12.006555</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-76.97411</t>
+          <t>-76.844143</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>219</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>292466</t>
+          <t>620043</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0032 RAUL PORRAS BARRENECHEA</t>
+          <t>CRUZ SACO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.05252</t>
+          <t>-12.07058</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-76.95082</t>
+          <t>-76.97704</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,37 +4097,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>292471</t>
+          <t>622075</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1143 DOMINGO FAUSTINO SARMIENTO</t>
+          <t>SANTA RITA DE ATE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.026228</t>
+          <t>-12.04023</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-76.918475</t>
+          <t>-76.87988</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>292485</t>
+          <t>651435</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>154 LOS CLAVELES</t>
+          <t>MI DULCE JESUS DE PRIALE</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.05247</t>
+          <t>-12.04377</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.94939</t>
+          <t>-76.89163</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>318</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>292490</t>
+          <t>718681</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1209 MARISCAL TORIBIO DE LUZURIAGA</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.07416</t>
+          <t>-12.05391</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-76.97915</t>
+          <t>-76.96043</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>292517</t>
+          <t>719987</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1208 SAN FRANCISCO DE ASIS</t>
+          <t>UNIMASTER</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.06484</t>
+          <t>-12.02784</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-76.96853</t>
+          <t>-76.93015</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4345,37 +4345,37 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>292522</t>
+          <t>747773</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>142 GRUMETE MEDINA</t>
+          <t>SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.06627</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-76.97233</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>386</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>292541</t>
+          <t>854701</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>KAROL WOJTYLA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.01402</t>
+          <t>-12.00694</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-76.81332</t>
+          <t>-76.84385</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>292555</t>
+          <t>293423</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>162 ANGELITOS DE JESUS</t>
+          <t>DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-12.01016</t>
+          <t>-12.03562</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-76.82864</t>
+          <t>-76.92829</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>244</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>292579</t>
+          <t>720085</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1260 EL AMAUTA</t>
+          <t>MAHATMA GANDHI</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.01836</t>
+          <t>-12.0274</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-76.81812</t>
+          <t>-76.90405</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>292598</t>
+          <t>720839</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1255 WALTER PEÑALOZA RAMELLA</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.01948</t>
+          <t>-12.03705</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-76.813</t>
+          <t>-76.82411</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>338</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>292602</t>
+          <t>293946</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>207 DIVINO NIÑO JESUS</t>
+          <t>JOHN DALTON</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.01405</t>
+          <t>-12.05543</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-76.81329</t>
+          <t>-76.94012</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,37 +4717,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>292640</t>
+          <t>751393</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1270 JUAN EL BAUTISTA</t>
+          <t>MIS PEQUEÑOS GENIOS</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.021898</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-76.816434</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4779,37 +4779,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>292678</t>
+          <t>824441</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>6039 FERNANDO CARBAJAL SEGURA</t>
+          <t>CIBERT UNI DE VITARTE</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.08358</t>
+          <t>-12.03265</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-76.98193</t>
+          <t>-76.93744</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>292683</t>
+          <t>854715</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>MARIA DE LAS MERCEDES DE SALAMANCA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.0443</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-76.9022</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>88</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4903,37 +4903,37 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>292701</t>
+          <t>294031</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SANTA MARIA VIRGEN DE LA CARIDAD</t>
+          <t>SANTA MARIA APOSTOL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.0063</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.83463</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4965,37 +4965,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>292782</t>
+          <t>294578</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FAMILIA DE NAZARETH</t>
+          <t>MATER CRISTHIE</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.06052</t>
+          <t>-12.02307</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-76.99519</t>
+          <t>-76.90034</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>292824</t>
+          <t>664862</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>INCA GARCILASO DE LA VEGA</t>
+          <t>INTERNACIONAL DEL PACIFICO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.0298</t>
+          <t>-12.01211</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-76.93921</t>
+          <t>-76.85382</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>332</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>292843</t>
+          <t>721669</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>SAN IGNACIO SCHOOL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.04122</t>
+          <t>-12.030403</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-76.93055</t>
+          <t>-76.935874</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>429</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>292923</t>
+          <t>292683</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SANTA ANGELA</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.08008</t>
+          <t>-12.0443</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-76.98645</t>
+          <t>-76.9022</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>458</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>293022</t>
+          <t>292843</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ROSA VICTORIA MARTICORENA</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.04835</t>
+          <t>-12.04122</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-76.93728</t>
+          <t>-76.93055</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>262</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,42 +5275,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>293036</t>
+          <t>624084</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SAN BENITO DE PALERMO</t>
+          <t>MASTER CIENCIAS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.03955</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-76.92607</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>161</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>293041</t>
+          <t>810571</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PASCUAL SACO OLIVEROS - LUMBRERAS</t>
+          <t>TRILCE DE SALAMANCA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.02865</t>
+          <t>-12.07899</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-76.93446</t>
+          <t>-76.98265</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>293121</t>
+          <t>292008</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ESTUDIO Y ENSEÑANZA SANTA ROSA S.C.</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.04061</t>
+          <t>-12.03228</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-76.928</t>
+          <t>-76.93907</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>628</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>293140</t>
+          <t>292348</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DE COCHARCAS</t>
+          <t>1231 JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-12.06874</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-76.99441</t>
+          <t>-76.97919</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>388</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>293201</t>
+          <t>720066</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>EL PARAISO</t>
+          <t>SACO OLIVEROS APEIRON</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.02666</t>
+          <t>-12.05513</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-76.90918</t>
+          <t>-76.95376</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>548</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>293244</t>
+          <t>292065</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>1283 OKINAWA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-12.02436</t>
+          <t>-12.04551</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-76.91658</t>
+          <t>-76.89125</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>769</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>293282</t>
+          <t>294267</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS</t>
+          <t>CRISTO SALVADOR</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.06981</t>
+          <t>-12.0786</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-76.98188</t>
+          <t>-76.98589</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>377</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>293376</t>
+          <t>564037</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>FRANCIS SCHAEFFER</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.02992</t>
+          <t>-12.02425</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-76.92962</t>
+          <t>-76.90161</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>295</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>293423</t>
+          <t>721235</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DOMINGO SAVIO</t>
+          <t>SANTA INES</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-12.03562</t>
+          <t>-12.00572</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-76.92829</t>
+          <t>-76.83351</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>504</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,27 +5833,27 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>293507</t>
+          <t>293201</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>EL PARAISO</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-12.03077</t>
+          <t>-12.02666</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-76.93765</t>
+          <t>-76.90918</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>492</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>293630</t>
+          <t>293507</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-12.0546</t>
+          <t>-12.03077</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-76.95729</t>
+          <t>-76.93765</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>443</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>293705</t>
+          <t>294050</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MARIA DE LA ENCARNACION</t>
+          <t>SALESIAN COLLEGE</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-12.07401</t>
+          <t>-12.01494</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-76.98563</t>
+          <t>-76.82418</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>560</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>293734</t>
+          <t>294314</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SANTA MARIA DEL CAMINO</t>
+          <t>EDUARDO PALACI</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-12.0725</t>
+          <t>-12.02598</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-76.97792</t>
+          <t>-76.89999</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>408</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6081,37 +6081,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>293871</t>
+          <t>548429</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>SACO OLIVEROS DE SALAMANCA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.06389</t>
+          <t>-12.08014</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-76.98306</t>
+          <t>-76.98015</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>506</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6143,37 +6143,37 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>293946</t>
+          <t>549221</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>JOHN DALTON</t>
+          <t>TECHNOLOGY SCHOOLS METROPOLITANA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-12.05543</t>
+          <t>-12.03317</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-76.94012</t>
+          <t>-76.9417</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>381</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6205,37 +6205,37 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>293965</t>
+          <t>554118</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MI UNIVERSO MAGICO</t>
+          <t>HOWARD GARDNER</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.02503</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.91338</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>276</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>294031</t>
+          <t>720820</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SANTA MARIA APOSTOL</t>
+          <t>1288 ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-12.0063</t>
+          <t>-12.02704</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-76.83463</t>
+          <t>-76.95171</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>664</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>294050</t>
+          <t>291990</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SALESIAN COLLEGE</t>
+          <t>0031 ROBERT F. KENNEDY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-12.01494</t>
+          <t>-12.0235</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-76.82418</t>
+          <t>-76.93579</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>485</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>294074</t>
+          <t>721787</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SANTIAGO APOSTOL</t>
+          <t>SANTA MARIA INTERNATIONAL SCHOOL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-12.02181</t>
+          <t>-12.03895</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-76.88455</t>
+          <t>-76.93109</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>769</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>294093</t>
+          <t>834992</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SANTA CATALINA</t>
+          <t>THALES DE SANTA CLARA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.04293</t>
+          <t>-12.01337</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-76.91546</t>
+          <t>-76.87966</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>294154</t>
+          <t>291725</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ALFRED NOBEL</t>
+          <t>1215 SAN JUAN PARIACHI</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.03812</t>
+          <t>-12.01066</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-76.91636</t>
+          <t>-76.8694</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>666</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>294173</t>
+          <t>292517</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ARCO IRIS</t>
+          <t>1208 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-12.0431</t>
+          <t>-12.06484</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-76.93536</t>
+          <t>-76.96853</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>564</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>294234</t>
+          <t>294540</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CORAZON DE GUADALUPE</t>
+          <t>MARIA RAFOLS</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-12.0161</t>
+          <t>-12.06258</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-76.824</t>
+          <t>-76.99097</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6701,42 +6701,42 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>294253</t>
+          <t>294899</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>JULIO RAMON RIBEYRO</t>
+          <t>RENE DESCARTES</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-12.0177368366089</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-76.9002549923646</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>534</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>294267</t>
+          <t>721527</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CRISTO SALVADOR</t>
+          <t>CIBERT UNI DE ATE VITARTE</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-12.0786</t>
+          <t>-12.03263</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-76.98589</t>
+          <t>-76.93733</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>759</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>294314</t>
+          <t>807173</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>EDUARDO PALACI</t>
+          <t>VILLA PROGRESO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-12.02598</t>
+          <t>-12.00744</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-76.89999</t>
+          <t>-76.833</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>489</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6887,37 +6887,37 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>294432</t>
+          <t>826299</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MUNDO MAGICO</t>
+          <t>CIBERT VITARTE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-12.02364</t>
+          <t>-12.031046</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-76.9115</t>
+          <t>-76.924433</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>749</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6949,42 +6949,42 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>294451</t>
+          <t>291834</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>JORGE CHAVEZ DARTNELL</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-12.06046</t>
+          <t>-12.02864</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-76.99577</t>
+          <t>-76.92962</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>580</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>294489</t>
+          <t>294093</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>JESUS MI BUEN PASTOR</t>
+          <t>SANTA CATALINA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-12.05277</t>
+          <t>-12.04293</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-76.95299</t>
+          <t>-76.91546</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>502</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>294535</t>
+          <t>621820</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MARIA REINA DE LOS APOSTOLES</t>
+          <t>SACO OLIVEROS DE ATE</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-12.0246</t>
+          <t>-12.05224</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-76.91198</t>
+          <t>-76.95291</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>655</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7135,42 +7135,42 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>294540</t>
+          <t>293871</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MARIA RAFOLS</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-12.06258</t>
+          <t>-12.06389</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-76.99097</t>
+          <t>-76.98306</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>294578</t>
+          <t>294173</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MATER CRISTHIE</t>
+          <t>ARCO IRIS</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-12.02307</t>
+          <t>-12.0431</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-76.90034</t>
+          <t>-76.93536</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>294601</t>
+          <t>526941</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SEÑOR CAUTIVO</t>
+          <t>SANTIAGO APOSTOL EL MAYOR</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7321,37 +7321,37 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>294639</t>
+          <t>548504</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-12.02141</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-76.82063</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>294682</t>
+          <t>655240</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LOS PORTALES DEL SABER</t>
+          <t>SIN FRONTERAS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-12.02718</t>
+          <t>-12.01382</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-76.92699</t>
+          <t>-76.87969</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7445,37 +7445,37 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>294861</t>
+          <t>818138</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HOGAR DE JESUS</t>
+          <t>MUNDO KIDS</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-12.06212</t>
+          <t>-12.027489</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-76.9971</t>
+          <t>-76.949351</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7507,37 +7507,37 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>294899</t>
+          <t>291787</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>RENE DESCARTES</t>
+          <t>1258 SEBASTIAN LORENTE</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.01452</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.82606</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>754</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>294979</t>
+          <t>292452</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 53</t>
+          <t>1212 GRUMETE MEDINA</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-12.007089</t>
+          <t>-12.06714</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-76.821257</t>
+          <t>-76.97411</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7631,37 +7631,37 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>294984</t>
+          <t>294535</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SANTA ANA</t>
+          <t>MARIA REINA DE LOS APOSTOLES</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.0246</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.91198</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7693,32 +7693,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>304902</t>
+          <t>292353</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>114 VIRGEN DE CHAPI</t>
+          <t>1203 DIVINO NIÑO JESUS DE MANYLSA</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-12.06214</t>
+          <t>-12.03163</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-76.98819</t>
+          <t>-76.88998</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>932</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7755,32 +7755,32 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>314656</t>
+          <t>292678</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ALTER CHRISTUS</t>
+          <t>6039 FERNANDO CARBAJAL SEGURA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-12.006555</t>
+          <t>-12.08358</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-76.844143</t>
+          <t>-76.98193</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>786</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>506245</t>
+          <t>292824</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>BOSTON HIGH SCHOOL</t>
+          <t>INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-12.00886</t>
+          <t>-12.0298</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-76.85425</t>
+          <t>-76.93921</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>577</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7879,37 +7879,37 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>523971</t>
+          <t>293121</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>THALES DE MILETO</t>
+          <t>ESTUDIO Y ENSEÑANZA SANTA ROSA S.C.</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.04061</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.928</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>398</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7941,37 +7941,37 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>523985</t>
+          <t>720660</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MIS PASITOS</t>
+          <t>AKIRA KATO</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.023037</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.837182</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>693</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8003,37 +8003,37 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>526941</t>
+          <t>291952</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SANTIAGO APOSTOL EL MAYOR</t>
+          <t>NUESTRA SEÑORA DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.07297</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.98454</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>511</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8065,32 +8065,32 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>548429</t>
+          <t>294074</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE SALAMANCA</t>
+          <t>SANTIAGO APOSTOL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-12.08014</t>
+          <t>-12.02181</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>-76.98015</t>
+          <t>-76.88455</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>843</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8127,37 +8127,37 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>548504</t>
+          <t>292070</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>1136 JOHN F. KENNEDY</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.07452</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.9871</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>676</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8189,37 +8189,37 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>549221</t>
+          <t>292466</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS METROPOLITANA</t>
+          <t>0032 RAUL PORRAS BARRENECHEA</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-12.03317</t>
+          <t>-12.05252</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>-76.9417</t>
+          <t>-76.95082</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>711</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8251,32 +8251,32 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>554118</t>
+          <t>292640</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>HOWARD GARDNER</t>
+          <t>1270 JUAN EL BAUTISTA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-12.02503</t>
+          <t>-12.021898</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>-76.91338</t>
+          <t>-76.816434</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>693</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8313,32 +8313,32 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>554986</t>
+          <t>293036</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SAN CRISTOBAL DE MONTEROSA</t>
+          <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-12.03601</t>
+          <t>-12.03955</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-76.9198</t>
+          <t>-76.92607</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>586</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8375,37 +8375,37 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>564037</t>
+          <t>846320</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FRANCIS SCHAEFFER</t>
+          <t>THALES DE VITARTE</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-12.02425</t>
+          <t>-12.02601</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>-76.90161</t>
+          <t>-76.90835</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>497</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8437,37 +8437,37 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>565536</t>
+          <t>721773</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>BEATITA TERESITA DE CALCUTA</t>
+          <t>1290 NUEVA AMERICA</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-12.03662</t>
+          <t>-12.039784</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-76.93239</t>
+          <t>-76.892046</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>946</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>592592</t>
+          <t>294451</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SANTA TERESA DE CALCUTA DE ATE</t>
+          <t>JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.06046</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.99577</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8561,37 +8561,37 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>615193</t>
+          <t>294601</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>SEÑOR CAUTIVO</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-12.00948</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-76.83477</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8623,37 +8623,37 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>617093</t>
+          <t>523985</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ANDINITO</t>
+          <t>MIS PASITOS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-12.02098</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>-76.87864</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8685,37 +8685,37 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>620043</t>
+          <t>819963</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CRUZ SACO</t>
+          <t>SANTA LUISA DE MARILLAC II</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-12.07058</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-76.97704</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>295</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8747,32 +8747,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>621820</t>
+          <t>291768</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE ATE</t>
+          <t>0074 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-12.05224</t>
+          <t>-12.07036</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>-76.95291</t>
+          <t>-76.98429</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>674</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8809,32 +8809,32 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>622075</t>
+          <t>291565</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SANTA RITA DE ATE</t>
+          <t>1252 SANTA ISABEL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-12.04023</t>
+          <t>-12.03596</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>-76.87988</t>
+          <t>-76.90168</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>863</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8871,37 +8871,37 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>624084</t>
+          <t>292305</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MASTER CIENCIAS</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.03072</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.88971</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>976</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8933,42 +8933,42 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>624531</t>
+          <t>294253</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MI CRISTO SALVADOR</t>
+          <t>JULIO RAMON RIBEYRO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.0177368366089</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.9002549923646</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>966</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8995,32 +8995,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>633007</t>
+          <t>291612</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>PAMER PARACAS</t>
+          <t>1263 PURUCHUCO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-12.08035</t>
+          <t>-12.04869</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>-76.97973</t>
+          <t>-76.93006</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>902</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9057,32 +9057,32 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>651402</t>
+          <t>291867</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GOTITAS DE AGUA</t>
+          <t>1245 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-12.02911</t>
+          <t>-12.01519</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>-76.90164</t>
+          <t>-76.82089</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>979</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9119,32 +9119,32 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>651435</t>
+          <t>835411</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MI DULCE JESUS DE PRIALE</t>
+          <t>INNOVA SCHOOLS - ATE SANTA MARIA</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-12.04377</t>
+          <t>-12.02748</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>-76.89163</t>
+          <t>-76.88939</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>722</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9181,32 +9181,32 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>655198</t>
+          <t>291706</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE JAVIER PRADO</t>
+          <t>0029 MARCO PUENTE LLANOS</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-12.03774</t>
+          <t>-12.0312</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-76.92382</t>
+          <t>-76.92155</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>914</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>655221</t>
+          <t>291914</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>LAS GARDENIAS</t>
+          <t>1229 CAP. JULIO A. PONCE ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-12.01465</t>
+          <t>-12.05782</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>-76.87034</t>
+          <t>-76.95716</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>989</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9305,32 +9305,32 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>655240</t>
+          <t>292131</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SIN FRONTERAS</t>
+          <t>1257 REINO UNIDO DE GRAN BRETAÑA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-12.01382</t>
+          <t>-12.01972</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-76.87969</t>
+          <t>-76.82682</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>915</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9367,32 +9367,32 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>664862</t>
+          <t>292089</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>INTERNACIONAL DEL PACIFICO</t>
+          <t>TELESFORO CATACORA</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-12.01211</t>
+          <t>-12.01954</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-76.85382</t>
+          <t>-76.8845</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>997</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9429,32 +9429,32 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>718515</t>
+          <t>291607</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ANDINO</t>
+          <t>1237 JORGE D. GILES LLANOS</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-12.020981</t>
+          <t>-12.01951</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-76.878487</t>
+          <t>-76.83795</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9491,32 +9491,32 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>718681</t>
+          <t>292409</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>1222 HUSARES DE JUNIN</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-12.05391</t>
+          <t>-12.03049</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-76.96043</t>
+          <t>-76.93735</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>719807</t>
+          <t>293705</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>CIENCIAS APLICADAS ALBERT EINSTEIN</t>
+          <t>MARIA DE LA ENCARNACION</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-12.011</t>
+          <t>-12.07401</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-76.82285</t>
+          <t>-76.98563</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>418</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9615,32 +9615,32 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>719987</t>
+          <t>722447</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>UNIMASTER</t>
+          <t>INNOVA SCHOOLS - PURUCHUCO</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-12.02784</t>
+          <t>-12.0429</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-76.93015</t>
+          <t>-76.93304</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9677,32 +9677,32 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>720066</t>
+          <t>294979</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS APEIRON</t>
+          <t>FE Y ALEGRIA 53</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-12.05513</t>
+          <t>-12.007089</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-76.95376</t>
+          <t>-76.821257</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9739,37 +9739,37 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>720085</t>
+          <t>293965</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>MAHATMA GANDHI</t>
+          <t>MI UNIVERSO MAGICO</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-12.0274</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-76.90405</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9801,37 +9801,37 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>720165</t>
+          <t>831700</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1236 ALFONSO BARRANTES LINGAN</t>
+          <t>MI MUNDO MAGICO REAL FELIPE</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-12.00963</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>-76.82848</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9863,37 +9863,37 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>720288</t>
+          <t>291631</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SALESIAN INNOVA</t>
+          <t>1262 EL AMAUTA JOSE C. MARIATEGUI</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-12.062</t>
+          <t>-12.04274</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>-76.99515</t>
+          <t>-76.89804</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9925,32 +9925,32 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>720349</t>
+          <t>854372</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>MARTIR DE LA MEDICINA DANIEL A. CARRION</t>
+          <t>INNOVA SCHOOLS - ATE MAYORAZGO</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>-12.00681</t>
+          <t>-12.0432</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>-76.84449</t>
+          <t>-76.93305</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9987,37 +9987,37 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>720373</t>
+          <t>291947</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>LAS AMERICAS DE ATE</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>-12.03475</t>
+          <t>-12.03692</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>-76.90406</t>
+          <t>-76.93268</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10049,32 +10049,32 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>720660</t>
+          <t>294639</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AKIRA KATO</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>-12.023037</t>
+          <t>-12.02141</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>-76.837182</t>
+          <t>-76.82063</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>853</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10111,32 +10111,32 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>720820</t>
+          <t>292329</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1288 ALBERT EINSTEIN</t>
+          <t>1244 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>-12.02704</t>
+          <t>-12.04625</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>-76.95171</t>
+          <t>-76.92868</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10173,32 +10173,32 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>720839</t>
+          <t>292579</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1260 EL AMAUTA</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>-12.03705</t>
+          <t>-12.01836</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>-76.82411</t>
+          <t>-76.81812</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -10235,42 +10235,42 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>720981</t>
+          <t>292310</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>TRILCE DE SALAMANCA</t>
+          <t>1138 JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>-12.08007</t>
+          <t>-12.0616</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>-76.98503</t>
+          <t>-76.99595</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -10297,37 +10297,37 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>721235</t>
+          <t>292471</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SANTA INES</t>
+          <t>1143 DOMINGO FAUSTINO SARMIENTO</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>-12.00572</t>
+          <t>-12.026228</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>-76.83351</t>
+          <t>-76.918475</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10359,32 +10359,32 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>721283</t>
+          <t>721990</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SELECCION A DE ATE</t>
+          <t>PACIFICO</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>-12.0281</t>
+          <t>-12.03653</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>-76.93807</t>
+          <t>-76.92356</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>347</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -10421,32 +10421,32 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>721527</t>
+          <t>725040</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CIBERT UNI DE ATE VITARTE</t>
+          <t>INNOVA SCHOOLS - VITARTE</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>-12.03263</t>
+          <t>-12.02798</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>-76.93733</t>
+          <t>-76.93862</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -10483,32 +10483,32 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>721669</t>
+          <t>294154</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SAN IGNACIO SCHOOL</t>
+          <t>ALFRED NOBEL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>-12.030403</t>
+          <t>-12.03812</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>-76.935874</t>
+          <t>-76.91636</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>959</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -10545,32 +10545,32 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>721773</t>
+          <t>294234</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>1290 NUEVA AMERICA</t>
+          <t>CORAZON DE GUADALUPE</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>-12.039784</t>
+          <t>-12.0161</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>-76.892046</t>
+          <t>-76.824</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -10607,32 +10607,32 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>721787</t>
+          <t>633007</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SANTA MARIA INTERNATIONAL SCHOOL</t>
+          <t>PAMER PARACAS</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>-12.03895</t>
+          <t>-12.08035</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>-76.93109</t>
+          <t>-76.97973</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>337</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -10669,22 +10669,22 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>721805</t>
+          <t>722126</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>LUCERITO DE AMOR</t>
+          <t>ENRIQUE PESTALOZZI</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>-12.01838</t>
+          <t>-12.01076</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>-76.88581</t>
+          <t>-76.85363</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -10731,42 +10731,42 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>721990</t>
+          <t>858577</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>PACIFICO</t>
+          <t>TESORITOS DE DIOS</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>-12.03653</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>-76.92356</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10793,37 +10793,37 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>722008</t>
+          <t>291848</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ROMEO LUNA VICTORIA</t>
+          <t>1251 PERUANO SUIZO</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.02194</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.8717</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10855,37 +10855,37 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>722126</t>
+          <t>292254</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ENRIQUE PESTALOZZI</t>
+          <t>046 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>-12.01076</t>
+          <t>-12.025984</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>-76.85363</t>
+          <t>-76.918236</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10917,32 +10917,32 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>722145</t>
+          <t>292923</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>LA CATOLICA REDEMPTORIS MATER</t>
+          <t>SANTA ANGELA</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>-12.03121</t>
+          <t>-12.08008</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>-76.88959</t>
+          <t>-76.98645</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>770</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10979,37 +10979,37 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>722254</t>
+          <t>291711</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA CRUZ</t>
+          <t>COLEGIO NACIONAL MIXTO HUAYCAN</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.01531</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.82682</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>722447</t>
+          <t>292367</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - PURUCHUCO</t>
+          <t>1227 INDIRA GANDHI</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>-12.0429</t>
+          <t>-12.03273</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>-76.93304</t>
+          <t>-76.9317</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -11103,32 +11103,32 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>725040</t>
+          <t>292273</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - VITARTE</t>
+          <t>0026 AICHI NAGOYA</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>-12.02798</t>
+          <t>-12.03073</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>-76.93862</t>
+          <t>-76.90986</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -11165,37 +11165,37 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>747773</t>
+          <t>720165</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>SEÑOR DE LOS MILAGROS</t>
+          <t>1236 ALFONSO BARRANTES LINGAN</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.00963</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.82848</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11227,37 +11227,37 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>751393</t>
+          <t>858332</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MIS PEQUEÑOS GENIOS</t>
+          <t>THALES</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.01347</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.821473</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>439</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11289,32 +11289,32 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>755027</t>
+          <t>292150</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>TARPUY MODERNO</t>
+          <t>COLEGIO NACIONAL VITARTE</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>-12.01185</t>
+          <t>-12.02587</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>-76.85059</t>
+          <t>-76.92445</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -11351,32 +11351,32 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>807173</t>
+          <t>292094</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>VILLA PROGRESO</t>
+          <t>JULIO C. TELLO</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>-12.00744</t>
+          <t>-12.03461</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>-76.833</t>
+          <t>-76.94043</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -11413,32 +11413,32 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>810571</t>
+          <t>292490</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>TRILCE DE SALAMANCA</t>
+          <t>1209 MARISCAL TORIBIO DE LUZURIAGA</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>-12.07899</t>
+          <t>-12.07416</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>-76.98265</t>
+          <t>-76.97915</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -11475,37 +11475,37 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>818138</t>
+          <t>291985</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>MUNDO KIDS</t>
+          <t>1264 JUAN ANDRES VIVANCO AMORIN</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>-12.027489</t>
+          <t>-12.04086</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>-76.949351</t>
+          <t>-76.92929</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11537,37 +11537,37 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>819963</t>
+          <t>293376</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SANTA LUISA DE MARILLAC II</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.02992</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.92962</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>311</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11599,32 +11599,32 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>824441</t>
+          <t>720288</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>CIBERT UNI DE VITARTE</t>
+          <t>SALESIAN INNOVA</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>-12.03265</t>
+          <t>-12.062</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>-76.93744</t>
+          <t>-76.99515</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -11661,32 +11661,32 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>826299</t>
+          <t>292428</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CIBERT VITARTE</t>
+          <t>1228 LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>-12.031046</t>
+          <t>-12.03599</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>-76.924433</t>
+          <t>-76.92746</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -11723,37 +11723,37 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>827524</t>
+          <t>292188</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>VILLA MARGARITA</t>
+          <t>0025 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.02624</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.90197</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11785,37 +11785,37 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>831700</t>
+          <t>292598</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MI MUNDO MAGICO REAL FELIPE</t>
+          <t>1255 WALTER PEÑALOZA RAMELLA</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.01948</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.813</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11847,37 +11847,37 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>834992</t>
+          <t>292701</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>THALES DE SANTA CLARA</t>
+          <t>SANTA MARIA VIRGEN DE LA CARIDAD</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>-12.01337</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>-76.87966</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11909,42 +11909,42 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>835411</t>
+          <t>292782</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - ATE SANTA MARIA</t>
+          <t>FAMILIA DE NAZARETH</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>-12.02748</t>
+          <t>-12.06052</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>-76.88939</t>
+          <t>-76.99519</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11971,37 +11971,37 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>846320</t>
+          <t>293282</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>THALES DE VITARTE</t>
+          <t>CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>-12.02601</t>
+          <t>-12.06981</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>-76.90835</t>
+          <t>-76.98188</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12033,37 +12033,37 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>854372</t>
+          <t>294432</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - ATE MAYORAZGO</t>
+          <t>MUNDO MAGICO</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>-12.0432</t>
+          <t>-12.02364</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>-76.93305</t>
+          <t>-76.9115</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>142</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -12095,37 +12095,37 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>854701</t>
+          <t>624531</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>KAROL WOJTYLA</t>
+          <t>MI CRISTO SALVADOR</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>-12.00694</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>-76.84385</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -12157,37 +12157,37 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>854715</t>
+          <t>291650</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>MARIA DE LAS MERCEDES DE SALAMANCA</t>
+          <t>192 SANTA ROSITA DE LIMA</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>-12.04855</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>-76.92995</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12219,32 +12219,32 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>854720</t>
+          <t>294984</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SALESIAN INNOVA SCHOOL</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>-12.014989</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>-76.838856</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>142</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -12281,32 +12281,32 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>858332</t>
+          <t>655221</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>THALES</t>
+          <t>LAS GARDENIAS</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>-12.01347</t>
+          <t>-12.01465</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>-76.821473</t>
+          <t>-76.87034</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -12343,12 +12343,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>858577</t>
+          <t>722008</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>TESORITOS DE DIOS</t>
+          <t>ROMEO LUNA VICTORIA</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -12363,12 +12363,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
@@ -1746,7 +1746,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BOSTON HIGH SCHOOL</t>
+          <t>IEP SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>565536</t>
+          <t>858577</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BEATITA TERESITA DE CALCUTA</t>
+          <t>TESORITOS DE DIOS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.03662</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.93239</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>722254</t>
+          <t>858332</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA CRUZ</t>
+          <t>THALES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>439</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-12.01347</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-76.821473</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>827524</t>
+          <t>854720</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VILLA MARGARITA</t>
+          <t>SALESIAN INNOVA SCHOOL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-12.014989</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-76.838856</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>292386</t>
+          <t>854715</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>MARIA DE LAS MERCEDES DE SALAMANCA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.03609</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.90103</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>292414</t>
+          <t>854701</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>210 MARIA PARADO DE BELLIDO</t>
+          <t>KAROL WOJTYLA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.04186</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.91925</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-12.00694</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.84385</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>617093</t>
+          <t>854372</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ANDINITO</t>
+          <t>INNOVA SCHOOLS - ATE MAYORAZGO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.02098</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.87864</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-12.0432</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.93305</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>291570</t>
+          <t>846320</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1281 SANTA MARIA</t>
+          <t>THALES DE VITARTE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.04287</t>
+          <t>497</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.92451</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>-12.02601</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.90835</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>291971</t>
+          <t>835411</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>171 VIRGEN DEL CARMEN</t>
+          <t>INNOVA SCHOOLS - ATE SANTA MARIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.02148</t>
+          <t>722</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.82385</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-12.02748</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.88939</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>292145</t>
+          <t>834992</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>137 LOS LAURELES</t>
+          <t>THALES DE SANTA CLARA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.02834</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.91694</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-12.01337</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.87966</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>292447</t>
+          <t>831700</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>189 SAGRADO CORAZON DE JESUS</t>
+          <t>MI MUNDO MAGICO REAL FELIPE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.0352</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.93764</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>292485</t>
+          <t>827524</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>154 LOS CLAVELES</t>
+          <t>VILLA MARGARITA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.05247</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.94939</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>294489</t>
+          <t>826299</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JESUS MI BUEN PASTOR</t>
+          <t>CIBERT VITARTE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.05277</t>
+          <t>749</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.95299</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-12.031046</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.924433</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>721283</t>
+          <t>824441</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SELECCION A DE ATE</t>
+          <t>CIBERT UNI DE VITARTE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.0281</t>
+          <t>56</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.93807</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>-12.03265</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.93744</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>854720</t>
+          <t>819963</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SALESIAN INNOVA SCHOOL</t>
+          <t>SANTA LUISA DE MARILLAC II</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.014989</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.838856</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>291688</t>
+          <t>818138</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>MUNDO KIDS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.02871</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.92471</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>-12.027489</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.949351</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>292112</t>
+          <t>810571</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>185 SEÑOR DE LOS MILAGROS</t>
+          <t>TRILCE DE SALAMANCA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.01815</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.81286</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>-12.07899</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.98265</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>292169</t>
+          <t>807173</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>195 ANGELITOS DE JESUS</t>
+          <t>VILLA PROGRESO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.02786</t>
+          <t>489</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.90741</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-12.00744</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.833</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>292522</t>
+          <t>755027</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>142 GRUMETE MEDINA</t>
+          <t>TARPUY MODERNO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.06627</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.97233</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-12.01185</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.85059</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>292602</t>
+          <t>751393</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>207 DIVINO NIÑO JESUS</t>
+          <t>MIS PEQUEÑOS GENIOS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.01405</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.81329</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>293041</t>
+          <t>747773</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PASCUAL SACO OLIVEROS - LUMBRERAS</t>
+          <t>SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.02865</t>
+          <t>386</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.93446</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>506245</t>
+          <t>725040</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IEP SEÑOR DE LOS MILAGROS</t>
+          <t>INNOVA SCHOOLS - VITARTE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.00886</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.85425</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>-12.02798</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.93862</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>291551</t>
+          <t>722447</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>164 JEAN PIAGET</t>
+          <t>INNOVA SCHOOLS - PURUCHUCO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.01357</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.83749</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>-12.0429</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.93304</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>291626</t>
+          <t>722254</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>NUESTRA SEÑORA DE LA CRUZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.04295</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.8978</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>291730</t>
+          <t>722145</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>500 EL BOSQUE</t>
+          <t>LA CATOLICA REDEMPTORIS MATER</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.06206</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.98335</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>-12.03121</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.88959</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>291810</t>
+          <t>722126</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1243 SAN ROQUE</t>
+          <t>ENRIQUE PESTALOZZI</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.02021</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.90614</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>-12.01076</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.85363</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>291933</t>
+          <t>722008</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1265 SANTA ROSA DE LIMA</t>
+          <t>ROMEO LUNA VICTORIA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.00932</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.816</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>292391</t>
+          <t>721990</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>168 MARIA EUGENIA MANTILLA ARIAS</t>
+          <t>PACIFICO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.0581261963589</t>
+          <t>347</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.9577655261935</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>-12.03653</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.92356</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>292555</t>
+          <t>721805</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>162 ANGELITOS DE JESUS</t>
+          <t>LUCERITO DE AMOR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.01016</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.82864</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>-12.01838</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.88581</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>293630</t>
+          <t>721787</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>SANTA MARIA INTERNATIONAL SCHOOL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.0546</t>
+          <t>769</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.95729</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>-12.03895</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.93109</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>294861</t>
+          <t>721773</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HOGAR DE JESUS</t>
+          <t>1290 NUEVA AMERICA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.06212</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.9971</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>-12.039784</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.892046</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>720981</t>
+          <t>721669</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TRILCE DE SALAMANCA</t>
+          <t>SAN IGNACIO SCHOOL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.08007</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.98503</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-12.030403</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.935874</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>291645</t>
+          <t>721527</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>CIBERT UNI DE ATE VITARTE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.04497</t>
+          <t>759</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.91523</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-12.03263</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.93733</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>291829</t>
+          <t>721283</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>135 NIÑO JESUS</t>
+          <t>SELECCION A DE ATE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.0733</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.98087</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-12.0281</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.93807</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>292433</t>
+          <t>721235</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>SANTA INES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.02895</t>
+          <t>504</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.92146</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-12.00572</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.83351</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>293022</t>
+          <t>720981</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ROSA VICTORIA MARTICORENA</t>
+          <t>TRILCE DE SALAMANCA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.04835</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.93728</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-12.08007</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.98503</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>293140</t>
+          <t>720839</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DE COCHARCAS</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>338</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.99441</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-12.03705</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.82411</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>615193</t>
+          <t>720820</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>1288 ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.00948</t>
+          <t>664</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.83477</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-12.02704</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.95171</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>655198</t>
+          <t>720660</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE JAVIER PRADO</t>
+          <t>AKIRA KATO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.03774</t>
+          <t>693</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.92382</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>-12.023037</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.837182</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2867,22 +2867,22 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>-12.03475</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>-76.90406</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>721805</t>
+          <t>720349</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LUCERITO DE AMOR</t>
+          <t>MARTIR DE LA MEDICINA DANIEL A. CARRION</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.01838</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.88581</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-12.00681</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.84449</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,37 +2981,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>722145</t>
+          <t>720288</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LA CATOLICA REDEMPTORIS MATER</t>
+          <t>SALESIAN INNOVA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.03121</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.88959</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-12.062</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.99515</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>755027</t>
+          <t>720165</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TARPUY MODERNO</t>
+          <t>1236 ALFONSO BARRANTES LINGAN</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.01185</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.85059</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>-12.00963</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.82848</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>291594</t>
+          <t>720085</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1249 JAVIER HERAUD</t>
+          <t>MAHATMA GANDHI</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.02791</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.91514</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-12.0274</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.90405</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>292051</t>
+          <t>720066</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>183 SANTA ROSITA DE MANYLSA</t>
+          <t>SACO OLIVEROS APEIRON</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.03071</t>
+          <t>548</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.88908</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>-12.05513</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.95376</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>294682</t>
+          <t>719987</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LOS PORTALES DEL SABER</t>
+          <t>UNIMASTER</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.02718</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.92699</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-12.02784</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.93015</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>651402</t>
+          <t>719807</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GOTITAS DE AGUA</t>
+          <t>CIENCIAS APLICADAS ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.02911</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.90164</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>-12.011</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.82285</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>720349</t>
+          <t>718681</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MARTIR DE LA MEDICINA DANIEL A. CARRION</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.00681</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.84449</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-12.05391</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.96043</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>292541</t>
+          <t>718515</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>ANDINO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.01402</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.81332</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>-12.020981</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.878487</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>293244</t>
+          <t>664862</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>INTERNACIONAL DEL PACIFICO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.02436</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.91658</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>-12.01211</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.85382</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>293734</t>
+          <t>655240</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SANTA MARIA DEL CAMINO</t>
+          <t>SIN FRONTERAS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.0725</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.97792</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-12.01382</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.87969</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,37 +3601,37 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>523971</t>
+          <t>655221</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>THALES DE MILETO</t>
+          <t>LAS GARDENIAS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>-12.01465</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.87034</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>554986</t>
+          <t>655198</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SAN CRISTOBAL DE MONTEROSA</t>
+          <t>SACO OLIVEROS DE JAVIER PRADO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.03601</t>
+          <t>347</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.9198</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-12.03774</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.92382</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>592592</t>
+          <t>651435</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SANTA TERESA DE CALCUTA DE ATE</t>
+          <t>MI DULCE JESUS DE PRIALE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-12.04377</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.89163</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>718515</t>
+          <t>651402</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ANDINO</t>
+          <t>GOTITAS DE AGUA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.020981</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.878487</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>-12.02911</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.90164</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>719807</t>
+          <t>633007</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CIENCIAS APLICADAS ALBERT EINSTEIN</t>
+          <t>PAMER PARACAS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.011</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.82285</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>-12.08035</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.97973</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,37 +3911,37 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>304902</t>
+          <t>624531</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>114 VIRGEN DE CHAPI</t>
+          <t>MI CRISTO SALVADOR</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.06214</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-76.98819</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3973,37 +3973,37 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>314656</t>
+          <t>624084</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ALTER CHRISTUS</t>
+          <t>MASTER CIENCIAS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.006555</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-76.844143</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>620043</t>
+          <t>622075</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CRUZ SACO</t>
+          <t>SANTA RITA DE ATE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.07058</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-76.97704</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>-12.04023</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.87988</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>622075</t>
+          <t>621820</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SANTA RITA DE ATE</t>
+          <t>SACO OLIVEROS DE ATE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.04023</t>
+          <t>655</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-76.87988</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-12.05224</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.95291</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>651435</t>
+          <t>620043</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MI DULCE JESUS DE PRIALE</t>
+          <t>CRUZ SACO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.04377</t>
+          <t>328</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.89163</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>-12.07058</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.97704</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>718681</t>
+          <t>617093</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>ANDINITO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.05391</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-76.96043</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-12.02098</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.87864</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>719987</t>
+          <t>615193</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UNIMASTER</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.02784</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-76.93015</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-12.00948</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.83477</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>747773</t>
+          <t>592592</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SEÑOR DE LOS MILAGROS</t>
+          <t>SANTA TERESA DE CALCUTA DE ATE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>-12.025933</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>-76.918729</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,37 +4407,37 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>854701</t>
+          <t>565536</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KAROL WOJTYLA</t>
+          <t>BEATITA TERESITA DE CALCUTA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.00694</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-76.84385</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-12.03662</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.93239</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>293423</t>
+          <t>564037</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>DOMINGO SAVIO</t>
+          <t>FRANCIS SCHAEFFER</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-12.03562</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-76.92829</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>-12.02425</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.90161</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>720085</t>
+          <t>554986</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MAHATMA GANDHI</t>
+          <t>SAN CRISTOBAL DE MONTEROSA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.0274</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-76.90405</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>-12.03601</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.9198</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>720839</t>
+          <t>554118</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>HOWARD GARDNER</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.03705</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-76.82411</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>-12.02503</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.91338</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,37 +4655,37 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>293946</t>
+          <t>549221</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>JOHN DALTON</t>
+          <t>TECHNOLOGY SCHOOLS METROPOLITANA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.05543</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-76.94012</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-12.03317</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.9417</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>751393</t>
+          <t>548504</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MIS PEQUEÑOS GENIOS</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
           <t>-12.025933</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>-76.918729</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,37 +4779,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>824441</t>
+          <t>548429</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CIBERT UNI DE VITARTE</t>
+          <t>SACO OLIVEROS DE SALAMANCA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.03265</t>
+          <t>506</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-76.93744</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-12.08014</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-76.98015</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>854715</t>
+          <t>526941</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MARIA DE LAS MERCEDES DE SALAMANCA</t>
+          <t>SANTIAGO APOSTOL EL MAYOR</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
           <t>-12.025933</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>-76.918729</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,37 +4903,37 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>294031</t>
+          <t>523985</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SANTA MARIA APOSTOL</t>
+          <t>MIS PASITOS</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.0063</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-76.83463</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4965,37 +4965,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>294578</t>
+          <t>523971</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MATER CRISTHIE</t>
+          <t>THALES DE MILETO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.02307</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-76.90034</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>664862</t>
+          <t>506245</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>INTERNACIONAL DEL PACIFICO</t>
+          <t>SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.01211</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-76.85382</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>-12.00886</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.85425</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>721669</t>
+          <t>314656</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SAN IGNACIO SCHOOL</t>
+          <t>ALTER CHRISTUS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.030403</t>
+          <t>219</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-76.935874</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>-12.006555</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.844143</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>292683</t>
+          <t>304902</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>114 VIRGEN DE CHAPI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.0443</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-76.9022</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>-12.06214</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.98819</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,37 +5213,37 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>292843</t>
+          <t>294984</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.04122</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-76.93055</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5275,37 +5275,37 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>624084</t>
+          <t>294979</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MASTER CIENCIAS</t>
+          <t>FE Y ALEGRIA 53</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>-12.007089</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.821257</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5337,37 +5337,37 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>810571</t>
+          <t>294899</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TRILCE DE SALAMANCA</t>
+          <t>RENE DESCARTES</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.07899</t>
+          <t>534</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-76.98265</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5399,37 +5399,37 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>292008</t>
+          <t>294861</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>HOGAR DE JESUS</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.03228</t>
+          <t>187</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-76.93907</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>-12.06212</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.9971</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>292348</t>
+          <t>294682</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1231 JOSE LUIS BUSTAMANTE Y RIVERO</t>
+          <t>LOS PORTALES DEL SABER</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-12.06874</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-76.97919</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>-12.02718</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.92699</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>720066</t>
+          <t>294639</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS APEIRON</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.05513</t>
+          <t>853</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-76.95376</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>-12.02141</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.82063</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,37 +5585,37 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>292065</t>
+          <t>294601</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1283 OKINAWA</t>
+          <t>SEÑOR CAUTIVO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-12.04551</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-76.89125</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>294267</t>
+          <t>294578</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CRISTO SALVADOR</t>
+          <t>MATER CRISTHIE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.0786</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-76.98589</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>-12.02307</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.90034</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>564037</t>
+          <t>294540</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FRANCIS SCHAEFFER</t>
+          <t>MARIA RAFOLS</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.02425</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-76.90161</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>-12.06258</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.99097</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>721235</t>
+          <t>294535</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SANTA INES</t>
+          <t>MARIA REINA DE LOS APOSTOLES</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-12.00572</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-76.83351</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>-12.0246</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.91198</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>293201</t>
+          <t>294489</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>EL PARAISO</t>
+          <t>JESUS MI BUEN PASTOR</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-12.02666</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-76.90918</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>-12.05277</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.95299</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5895,37 +5895,37 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>293507</t>
+          <t>294451</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-12.03077</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-76.93765</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>-12.06046</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.99577</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5957,37 +5957,37 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>294050</t>
+          <t>294432</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SALESIAN COLLEGE</t>
+          <t>MUNDO MAGICO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-12.01494</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-76.82418</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>-12.02364</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.9115</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6029,22 +6029,22 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
           <t>-12.02598</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>-76.89999</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>548429</t>
+          <t>294267</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE SALAMANCA</t>
+          <t>CRISTO SALVADOR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.08014</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-76.98015</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>-12.0786</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.98589</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6143,42 +6143,42 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>549221</t>
+          <t>294253</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS METROPOLITANA</t>
+          <t>JULIO RAMON RIBEYRO</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-12.03317</t>
+          <t>966</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-76.9417</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>-12.0177368366089</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.9002549923646</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>554118</t>
+          <t>294234</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HOWARD GARDNER</t>
+          <t>CORAZON DE GUADALUPE</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-12.02503</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-76.91338</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>-12.0161</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.824</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>720820</t>
+          <t>294173</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1288 ALBERT EINSTEIN</t>
+          <t>ARCO IRIS</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-12.02704</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-76.95171</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>-12.0431</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.93536</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>291990</t>
+          <t>294154</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0031 ROBERT F. KENNEDY</t>
+          <t>ALFRED NOBEL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-12.0235</t>
+          <t>959</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-76.93579</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>-12.03812</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.91636</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>721787</t>
+          <t>294093</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SANTA MARIA INTERNATIONAL SCHOOL</t>
+          <t>SANTA CATALINA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-12.03895</t>
+          <t>502</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-76.93109</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>-12.04293</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.91546</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>834992</t>
+          <t>294074</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>THALES DE SANTA CLARA</t>
+          <t>SANTIAGO APOSTOL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.01337</t>
+          <t>843</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-76.87966</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-12.02181</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.88455</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>291725</t>
+          <t>294050</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1215 SAN JUAN PARIACHI</t>
+          <t>SALESIAN COLLEGE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.01066</t>
+          <t>560</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-76.8694</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>-12.01494</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.82418</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>292517</t>
+          <t>294031</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1208 SAN FRANCISCO DE ASIS</t>
+          <t>SANTA MARIA APOSTOL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-12.06484</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-76.96853</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>-12.0063</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.83463</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6639,42 +6639,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>294540</t>
+          <t>293965</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MARIA RAFOLS</t>
+          <t>MI UNIVERSO MAGICO</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-12.06258</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-76.99097</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6701,37 +6701,37 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>294899</t>
+          <t>293946</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RENE DESCARTES</t>
+          <t>JOHN DALTON</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>-12.05543</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.94012</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6763,37 +6763,37 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>721527</t>
+          <t>293871</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CIBERT UNI DE ATE VITARTE</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-12.03263</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-76.93733</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>-12.06389</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.98306</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>807173</t>
+          <t>293734</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>VILLA PROGRESO</t>
+          <t>SANTA MARIA DEL CAMINO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-12.00744</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-76.833</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>-12.0725</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.97792</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>826299</t>
+          <t>293705</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CIBERT VITARTE</t>
+          <t>MARIA DE LA ENCARNACION</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-12.031046</t>
+          <t>418</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-76.924433</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>-12.07401</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.98563</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>291834</t>
+          <t>293630</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-12.02864</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-76.92962</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>-12.0546</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.95729</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>294093</t>
+          <t>293507</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SANTA CATALINA</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-12.04293</t>
+          <t>443</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-76.91546</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>-12.03077</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.93765</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>621820</t>
+          <t>293423</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE ATE</t>
+          <t>DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-12.05224</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-76.95291</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>-12.03562</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.92829</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7135,37 +7135,37 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>293871</t>
+          <t>293376</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-12.06389</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-76.98306</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-12.02992</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.92962</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>294173</t>
+          <t>293282</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ARCO IRIS</t>
+          <t>CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-12.0431</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-76.93536</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-12.06981</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.98188</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7259,37 +7259,37 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>526941</t>
+          <t>293244</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SANTIAGO APOSTOL EL MAYOR</t>
+          <t>SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-12.02436</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.91658</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7321,42 +7321,42 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>548504</t>
+          <t>293201</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>EL PARAISO</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>492</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-12.02666</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.90918</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>655240</t>
+          <t>293140</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SIN FRONTERAS</t>
+          <t>SANTISIMA VIRGEN DE COCHARCAS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-12.01382</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-76.87969</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.99441</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7445,37 +7445,37 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>818138</t>
+          <t>293121</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MUNDO KIDS</t>
+          <t>ESTUDIO Y ENSEÑANZA SANTA ROSA S.C.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-12.027489</t>
+          <t>398</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-76.949351</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-12.04061</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.928</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>291787</t>
+          <t>293041</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1258 SEBASTIAN LORENTE</t>
+          <t>PASCUAL SACO OLIVEROS - LUMBRERAS</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-12.01452</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-76.82606</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>-12.02865</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.93446</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>292452</t>
+          <t>293036</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1212 GRUMETE MEDINA</t>
+          <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-12.06714</t>
+          <t>586</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-76.97411</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>-12.03955</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.92607</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7631,32 +7631,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>294535</t>
+          <t>293022</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MARIA REINA DE LOS APOSTOLES</t>
+          <t>ROSA VICTORIA MARTICORENA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-12.0246</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-76.91198</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-12.04835</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.93728</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7693,32 +7693,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>292353</t>
+          <t>292923</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1203 DIVINO NIÑO JESUS DE MANYLSA</t>
+          <t>SANTA ANGELA</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-12.03163</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-76.88998</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>-12.08008</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.98645</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7755,32 +7755,32 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>292678</t>
+          <t>292843</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>6039 FERNANDO CARBAJAL SEGURA</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-12.08358</t>
+          <t>262</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-76.98193</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>-12.04122</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.93055</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7827,22 +7827,22 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
           <t>-12.0298</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t>-76.93921</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7879,37 +7879,37 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>293121</t>
+          <t>292782</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ESTUDIO Y ENSEÑANZA SANTA ROSA S.C.</t>
+          <t>FAMILIA DE NAZARETH</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-12.04061</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-76.928</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>-12.06052</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.99519</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7941,37 +7941,37 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>720660</t>
+          <t>292701</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AKIRA KATO</t>
+          <t>SANTA MARIA VIRGEN DE LA CARIDAD</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-12.023037</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-76.837182</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>-12.025933</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.918729</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8003,32 +8003,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>291952</t>
+          <t>292683</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA ESPERANZA</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-12.07297</t>
+          <t>458</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-76.98454</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>-12.0443</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.9022</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8065,32 +8065,32 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>294074</t>
+          <t>292678</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SANTIAGO APOSTOL</t>
+          <t>6039 FERNANDO CARBAJAL SEGURA</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-12.02181</t>
+          <t>786</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>-76.88455</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>-12.08358</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-76.98193</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>292070</t>
+          <t>292640</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1136 JOHN F. KENNEDY</t>
+          <t>1270 JUAN EL BAUTISTA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-12.07452</t>
+          <t>693</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>-76.9871</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>-12.021898</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-76.816434</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8189,32 +8189,32 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>292466</t>
+          <t>292602</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>0032 RAUL PORRAS BARRENECHEA</t>
+          <t>207 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-12.05252</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>-76.95082</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>-12.01405</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.81329</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8251,32 +8251,32 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>292640</t>
+          <t>292598</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1270 JUAN EL BAUTISTA</t>
+          <t>1255 WALTER PEÑALOZA RAMELLA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-12.021898</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>-76.816434</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>-12.01948</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.813</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8313,32 +8313,32 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>293036</t>
+          <t>292579</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SAN BENITO DE PALERMO</t>
+          <t>1260 EL AMAUTA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-12.03955</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-76.92607</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>-12.01836</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.81812</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8375,37 +8375,37 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>846320</t>
+          <t>292555</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>THALES DE VITARTE</t>
+          <t>162 ANGELITOS DE JESUS</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-12.02601</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>-76.90835</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>-12.01016</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.82864</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>721773</t>
+          <t>292541</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1290 NUEVA AMERICA</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-12.039784</t>
+          <t>447</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-76.892046</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>-12.01402</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.81332</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8499,37 +8499,37 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>294451</t>
+          <t>292522</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JORGE CHAVEZ DARTNELL</t>
+          <t>142 GRUMETE MEDINA</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-12.06046</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>-76.99577</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-12.06627</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.97233</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8561,42 +8561,42 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>294601</t>
+          <t>292517</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SEÑOR CAUTIVO</t>
+          <t>1208 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>564</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-12.06484</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.96853</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8623,37 +8623,37 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>523985</t>
+          <t>292490</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MIS PASITOS</t>
+          <t>1209 MARISCAL TORIBIO DE LUZURIAGA</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-12.07416</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.97915</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8685,37 +8685,37 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>819963</t>
+          <t>292485</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SANTA LUISA DE MARILLAC II</t>
+          <t>154 LOS CLAVELES</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>-12.05247</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.94939</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8747,42 +8747,42 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>291768</t>
+          <t>292471</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>0074 FERNANDO BELAUNDE TERRY</t>
+          <t>1143 DOMINGO FAUSTINO SARMIENTO</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-12.07036</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>-76.98429</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>-12.026228</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-76.918475</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8809,32 +8809,32 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>291565</t>
+          <t>292466</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>1252 SANTA ISABEL</t>
+          <t>0032 RAUL PORRAS BARRENECHEA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-12.03596</t>
+          <t>711</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>-76.90168</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>-12.05252</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-76.95082</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8871,32 +8871,32 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>292305</t>
+          <t>292452</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>1212 GRUMETE MEDINA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-12.03072</t>
+          <t>512</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>-76.88971</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>-12.06714</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-76.97411</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8933,32 +8933,32 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>294253</t>
+          <t>292447</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>JULIO RAMON RIBEYRO</t>
+          <t>189 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-12.0177368366089</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-76.9002549923646</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>-12.0352</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-76.93764</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8995,32 +8995,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>291612</t>
+          <t>292433</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>1263 PURUCHUCO</t>
+          <t>151</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-12.04869</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>-76.93006</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>-12.02895</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-76.92146</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9057,32 +9057,32 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>291867</t>
+          <t>292428</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1245 JOSE CARLOS MARIATEGUI</t>
+          <t>1228 LEONCIO PRADO</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-12.01519</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>-76.82089</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>-12.03599</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-76.92746</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9119,32 +9119,32 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>835411</t>
+          <t>292414</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - ATE SANTA MARIA</t>
+          <t>210 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-12.02748</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>-76.88939</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>-12.04186</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-76.91925</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9181,32 +9181,32 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>291706</t>
+          <t>292409</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>0029 MARCO PUENTE LLANOS</t>
+          <t>1222 HUSARES DE JUNIN</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-12.0312</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-76.92155</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>-12.03049</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-76.93735</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>291914</t>
+          <t>292391</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>1229 CAP. JULIO A. PONCE ANTUNEZ DE MAYOLO</t>
+          <t>168 MARIA EUGENIA MANTILLA ARIAS</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-12.05782</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>-76.95716</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>-12.0581261963589</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-76.9577655261935</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9305,32 +9305,32 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>292131</t>
+          <t>292386</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>1257 REINO UNIDO DE GRAN BRETAÑA</t>
+          <t>182</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-12.01972</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-76.82682</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>-12.03609</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-76.90103</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9367,32 +9367,32 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>292089</t>
+          <t>292367</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>TELESFORO CATACORA</t>
+          <t>1227 INDIRA GANDHI</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-12.01954</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-76.8845</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>-12.03273</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-76.9317</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9429,32 +9429,32 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>291607</t>
+          <t>292353</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>1237 JORGE D. GILES LLANOS</t>
+          <t>1203 DIVINO NIÑO JESUS DE MANYLSA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-12.01951</t>
+          <t>932</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-76.83795</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>-12.03163</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-76.88998</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9491,32 +9491,32 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>292409</t>
+          <t>292348</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>1222 HUSARES DE JUNIN</t>
+          <t>1231 JOSE LUIS BUSTAMANTE Y RIVERO</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-12.03049</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-76.93735</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>-12.06874</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-76.97919</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9553,32 +9553,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>293705</t>
+          <t>292329</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MARIA DE LA ENCARNACION</t>
+          <t>1244 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-12.07401</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-76.98563</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>-12.04625</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-76.92868</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9615,42 +9615,42 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>722447</t>
+          <t>292310</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - PURUCHUCO</t>
+          <t>1138 JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-12.0429</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-76.93304</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>-12.0616</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-76.99595</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9677,32 +9677,32 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>294979</t>
+          <t>292305</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 53</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-12.007089</t>
+          <t>976</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-76.821257</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>-12.03072</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-76.88971</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9739,37 +9739,37 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>293965</t>
+          <t>292273</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>MI UNIVERSO MAGICO</t>
+          <t>0026 AICHI NAGOYA</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-12.03073</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.90986</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9801,32 +9801,32 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>831700</t>
+          <t>292254</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>MI MUNDO MAGICO REAL FELIPE</t>
+          <t>046 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-12.025984</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.918236</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9863,32 +9863,32 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>291631</t>
+          <t>292188</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>1262 EL AMAUTA JOSE C. MARIATEGUI</t>
+          <t>0025 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-12.04274</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>-76.89804</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>-12.02624</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-76.90197</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9925,32 +9925,32 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>854372</t>
+          <t>292169</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - ATE MAYORAZGO</t>
+          <t>195 ANGELITOS DE JESUS</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>-12.0432</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>-76.93305</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>-12.02786</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-76.90741</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9987,37 +9987,37 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>291947</t>
+          <t>292150</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>COLEGIO NACIONAL VITARTE</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>-12.03692</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>-76.93268</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>-12.02587</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-76.92445</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10049,32 +10049,32 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>294639</t>
+          <t>292145</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>137 LOS LAURELES</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>-12.02141</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>-76.82063</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>-12.02834</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-76.91694</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10111,32 +10111,32 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>292329</t>
+          <t>292131</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1244 MICAELA BASTIDAS</t>
+          <t>1257 REINO UNIDO DE GRAN BRETAÑA</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>-12.04625</t>
+          <t>915</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>-76.92868</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>-12.01972</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-76.82682</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10173,32 +10173,32 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>292579</t>
+          <t>292112</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1260 EL AMAUTA</t>
+          <t>185 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>-12.01836</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>-76.81812</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>-12.01815</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-76.81286</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -10235,42 +10235,42 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>292310</t>
+          <t>292094</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1138 JOSE ABELARDO QUIÑONES</t>
+          <t>JULIO C. TELLO</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>-12.0616</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>-76.99595</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>-12.03461</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-76.94043</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10297,37 +10297,37 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>292471</t>
+          <t>292089</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>1143 DOMINGO FAUSTINO SARMIENTO</t>
+          <t>TELESFORO CATACORA</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>-12.026228</t>
+          <t>997</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>-76.918475</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>-12.01954</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-76.8845</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10359,32 +10359,32 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>721990</t>
+          <t>292070</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>PACIFICO</t>
+          <t>1136 JOHN F. KENNEDY</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>-12.03653</t>
+          <t>676</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>-76.92356</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>-12.07452</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-76.9871</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10421,32 +10421,32 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>725040</t>
+          <t>292065</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - VITARTE</t>
+          <t>1283 OKINAWA</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>-12.02798</t>
+          <t>769</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>-76.93862</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>-12.04551</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-76.89125</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -10483,32 +10483,32 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>294154</t>
+          <t>292051</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ALFRED NOBEL</t>
+          <t>183 SANTA ROSITA DE MANYLSA</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>-12.03812</t>
+          <t>367</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>-76.91636</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>-12.03071</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-76.88908</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -10545,32 +10545,32 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>294234</t>
+          <t>292008</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CORAZON DE GUADALUPE</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>-12.0161</t>
+          <t>628</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>-76.824</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-12.03228</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.93907</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -10607,32 +10607,32 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>633007</t>
+          <t>291990</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>PAMER PARACAS</t>
+          <t>0031 ROBERT F. KENNEDY</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>-12.08035</t>
+          <t>485</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>-76.97973</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>-12.0235</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.93579</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -10669,32 +10669,32 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>722126</t>
+          <t>291985</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ENRIQUE PESTALOZZI</t>
+          <t>1264 JUAN ANDRES VIVANCO AMORIN</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>-12.01076</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>-76.85363</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-12.04086</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.92929</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -10731,37 +10731,37 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>858577</t>
+          <t>291971</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>TESORITOS DE DIOS</t>
+          <t>171 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-12.02148</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.82385</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10793,32 +10793,32 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>291848</t>
+          <t>291952</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>1251 PERUANO SUIZO</t>
+          <t>NUESTRA SEÑORA DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>-12.02194</t>
+          <t>511</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>-76.8717</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>-12.07297</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-76.98454</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10855,32 +10855,32 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>292254</t>
+          <t>291947</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>046 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>-12.025984</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>-76.918236</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>-12.03692</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-76.93268</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10917,32 +10917,32 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>292923</t>
+          <t>291933</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SANTA ANGELA</t>
+          <t>1265 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>-12.08008</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>-76.98645</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>-12.00932</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-76.816</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10979,32 +10979,32 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>291711</t>
+          <t>291914</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>COLEGIO NACIONAL MIXTO HUAYCAN</t>
+          <t>1229 CAP. JULIO A. PONCE ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>-12.01531</t>
+          <t>989</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>-76.82682</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>-12.05782</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-76.95716</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>292367</t>
+          <t>291867</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>1227 INDIRA GANDHI</t>
+          <t>1245 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>-12.03273</t>
+          <t>979</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>-76.9317</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>-12.01519</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-76.82089</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -11103,32 +11103,32 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>292273</t>
+          <t>291848</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0026 AICHI NAGOYA</t>
+          <t>1251 PERUANO SUIZO</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>-12.03073</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>-76.90986</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>-12.02194</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-76.8717</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -11165,32 +11165,32 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>720165</t>
+          <t>291834</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>1236 ALFONSO BARRANTES LINGAN</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>-12.00963</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>-76.82848</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>-12.02864</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-76.92962</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -11227,32 +11227,32 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>858332</t>
+          <t>291829</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>THALES</t>
+          <t>135 NIÑO JESUS</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>-12.01347</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>-76.821473</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>-12.0733</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-76.98087</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11289,32 +11289,32 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>292150</t>
+          <t>291810</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>COLEGIO NACIONAL VITARTE</t>
+          <t>1243 SAN ROQUE</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>-12.02587</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>-76.92445</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>-12.02021</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-76.90614</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -11351,32 +11351,32 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>292094</t>
+          <t>291787</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>JULIO C. TELLO</t>
+          <t>1258 SEBASTIAN LORENTE</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>-12.03461</t>
+          <t>754</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>-76.94043</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>-12.01452</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-76.82606</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -11413,32 +11413,32 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>292490</t>
+          <t>291768</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>1209 MARISCAL TORIBIO DE LUZURIAGA</t>
+          <t>0074 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>-12.07416</t>
+          <t>674</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>-76.97915</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>-12.07036</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-76.98429</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -11475,32 +11475,32 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>291985</t>
+          <t>291730</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>1264 JUAN ANDRES VIVANCO AMORIN</t>
+          <t>500 EL BOSQUE</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>-12.04086</t>
+          <t>361</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>-76.92929</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>-12.06206</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-76.98335</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -11537,32 +11537,32 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>293376</t>
+          <t>291725</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>1215 SAN JUAN PARIACHI</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>-12.02992</t>
+          <t>666</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>-76.92962</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>-12.01066</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-76.8694</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -11599,37 +11599,37 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>720288</t>
+          <t>291711</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>SALESIAN INNOVA</t>
+          <t>COLEGIO NACIONAL MIXTO HUAYCAN</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>-12.062</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>-76.99515</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-12.01531</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-76.82682</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11661,32 +11661,32 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>292428</t>
+          <t>291706</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>1228 LEONCIO PRADO</t>
+          <t>0029 MARCO PUENTE LLANOS</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>-12.03599</t>
+          <t>914</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>-76.92746</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>-12.0312</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-76.92155</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11723,32 +11723,32 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>292188</t>
+          <t>291688</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>0025 SAN MARTIN DE PORRES</t>
+          <t>134</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>-12.02624</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>-76.90197</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>-12.02871</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-76.92471</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -11785,32 +11785,32 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>292598</t>
+          <t>291650</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>1255 WALTER PEÑALOZA RAMELLA</t>
+          <t>192 SANTA ROSITA DE LIMA</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>-12.01948</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>-76.813</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>-12.04855</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>-76.92995</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -11847,37 +11847,37 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>292701</t>
+          <t>291645</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SANTA MARIA VIRGEN DE LA CARIDAD</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-12.04497</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-76.91523</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11909,37 +11909,37 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>292782</t>
+          <t>291631</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FAMILIA DE NAZARETH</t>
+          <t>1262 EL AMAUTA JOSE C. MARIATEGUI</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>-12.06052</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>-76.99519</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-12.04274</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-76.89804</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11971,32 +11971,32 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>293282</t>
+          <t>291626</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>-12.06981</t>
+          <t>335</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>-76.98188</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-12.04295</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-76.8978</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -12033,37 +12033,37 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>294432</t>
+          <t>291612</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>MUNDO MAGICO</t>
+          <t>1263 PURUCHUCO</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>-12.02364</t>
+          <t>902</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>-76.9115</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>-12.04869</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-76.93006</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -12095,37 +12095,37 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>624531</t>
+          <t>291607</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>MI CRISTO SALVADOR</t>
+          <t>1237 JORGE D. GILES LLANOS</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-12.01951</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-76.83795</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -12157,32 +12157,32 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>291650</t>
+          <t>291594</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>192 SANTA ROSITA DE LIMA</t>
+          <t>1249 JAVIER HERAUD</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>-12.04855</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>-76.92995</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-12.02791</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.91514</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -12219,37 +12219,37 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>294984</t>
+          <t>291570</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SANTA ANA</t>
+          <t>1281 SANTA MARIA</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>301</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>-12.04287</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.92451</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12281,32 +12281,32 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>655221</t>
+          <t>291565</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>LAS GARDENIAS</t>
+          <t>1252 SANTA ISABEL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>-12.01465</t>
+          <t>863</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>-76.87034</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-12.03596</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.90168</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -12343,37 +12343,37 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>722008</t>
+          <t>291551</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ROMEO LUNA VICTORIA</t>
+          <t>164 JEAN PIAGET</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>-12.025933</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>-76.918729</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>-12.01357</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.83749</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-ATE.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
